--- a/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
+++ b/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
@@ -84,6 +84,11 @@
       <color rgb="FF000000" tint="0"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000" tint="0"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -102,6 +107,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
         <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -299,6 +310,20 @@
         <color rgb="FFD0D7E5"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7E5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -337,15 +362,19 @@
       <alignment wrapText="1" vertical="center" horizontal="right"/>
       <protection locked="1" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyFont="1" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="8" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1" applyFont="1" xfId="0">
       <alignment wrapText="1" vertical="center" horizontal="right"/>
       <protection locked="1" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="11" borderId="9" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1" applyFont="1" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="9" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyFont="1" xfId="0">
       <alignment wrapText="1" vertical="center" horizontal="right"/>
       <protection locked="1" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="10" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyFont="1" xfId="0">
+      <alignment wrapText="1" vertical="center" horizontal="right"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="11" applyFill="1" applyProtection="1" applyBorder="1" applyAlignment="1" applyFont="1" xfId="0">
       <alignment wrapText="1" vertical="center" horizontal="right"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -643,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z76"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.62109375"/>
@@ -850,16 +879,16 @@
       <c r="K2" s="9">
         <v>6.096</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="9">
         <v>19.1</v>
       </c>
       <c r="M2" s="9">
         <v>10490</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>5.91239763594603</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="10">
         <v>27</v>
       </c>
       <c r="P2" s="9">
@@ -870,7 +899,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="10">
         <v>48</v>
       </c>
       <c r="U2" s="5" t="inlineStr">
@@ -878,12 +907,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -938,22 +967,22 @@
       <c r="K3" s="9">
         <v>8.2296</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>20.8</v>
       </c>
       <c r="M3" s="9">
         <v>13250</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>7.61106010654548</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="10">
         <v>46</v>
       </c>
       <c r="P3" s="9">
         <v>19.9</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="9">
         <v>0.4545</v>
       </c>
       <c r="R3" s="5" t="inlineStr">
@@ -961,7 +990,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S3" s="9">
+      <c r="S3" s="10">
         <v>42</v>
       </c>
       <c r="U3" s="5" t="inlineStr">
@@ -969,12 +998,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1029,22 +1058,22 @@
       <c r="K4" s="9">
         <v>12.192</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>14</v>
       </c>
       <c r="M4" s="9">
         <v>15370</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>8.93932597090552</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="10">
         <v>66</v>
       </c>
       <c r="P4" s="9">
         <v>14.2</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="9">
         <v>0.8445</v>
       </c>
       <c r="R4" s="5" t="inlineStr">
@@ -1052,7 +1081,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S4" s="9">
+      <c r="S4" s="10">
         <v>51</v>
       </c>
       <c r="U4" s="5" t="inlineStr">
@@ -1060,12 +1089,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr">
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1120,22 +1149,22 @@
       <c r="K5" s="9">
         <v>11.5824</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>9.1</v>
       </c>
       <c r="M5" s="9">
         <v>517</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="9">
         <v>0.233956419909353</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="10">
         <v>17</v>
       </c>
       <c r="P5" s="9">
         <v>72.7</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="9">
         <v>2.4489</v>
       </c>
       <c r="R5" s="5" t="inlineStr">
@@ -1143,7 +1172,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S5" s="9">
+      <c r="S5" s="10">
         <v>68</v>
       </c>
       <c r="U5" s="5" t="inlineStr">
@@ -1151,12 +1180,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr">
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1211,22 +1240,22 @@
       <c r="K6" s="9">
         <v>11.8872</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>10.5</v>
       </c>
       <c r="M6" s="9">
         <v>640</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>0.29</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="10">
         <v>43</v>
       </c>
       <c r="P6" s="9">
         <v>28</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="9">
         <v>1.4267</v>
       </c>
       <c r="R6" s="5" t="inlineStr">
@@ -1234,7 +1263,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S6" s="9">
+      <c r="S6" s="10">
         <v>57</v>
       </c>
       <c r="U6" s="5" t="inlineStr">
@@ -1242,12 +1271,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr">
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1302,22 +1331,22 @@
       <c r="K7" s="9">
         <v>6.096</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>12.8</v>
       </c>
       <c r="M7" s="9">
         <v>1170</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <v>0.56</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="10">
         <v>20</v>
       </c>
       <c r="P7" s="9">
         <v>117</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="9">
         <v>3.0327</v>
       </c>
       <c r="R7" s="5" t="inlineStr">
@@ -1325,7 +1354,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S7" s="9">
+      <c r="S7" s="10">
         <v>75</v>
       </c>
       <c r="U7" s="5" t="inlineStr">
@@ -1333,12 +1362,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1393,22 +1422,22 @@
       <c r="K8" s="9">
         <v>6.096</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>12.8</v>
       </c>
       <c r="M8" s="9">
         <v>1170</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>0.56</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="10">
         <v>20</v>
       </c>
       <c r="P8" s="9">
         <v>117</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="9">
         <v>3.0301</v>
       </c>
       <c r="R8" s="5" t="inlineStr">
@@ -1416,7 +1445,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S8" s="9">
+      <c r="S8" s="10">
         <v>72</v>
       </c>
       <c r="U8" s="5" t="inlineStr">
@@ -1424,12 +1453,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr">
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1484,22 +1513,22 @@
       <c r="K9" s="9">
         <v>9.4488</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>12.5</v>
       </c>
       <c r="M9" s="9">
         <v>174</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <v>0.07</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <v>81</v>
       </c>
       <c r="P9" s="9">
         <v>47</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="9">
         <v>1.8383</v>
       </c>
       <c r="R9" s="5" t="inlineStr">
@@ -1507,7 +1536,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="10">
         <v>69</v>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -1515,12 +1544,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1575,22 +1604,22 @@
       <c r="K10" s="9">
         <v>12.8016</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>13.4</v>
       </c>
       <c r="M10" s="9">
         <v>312</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>0.14</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="10">
         <v>34</v>
       </c>
       <c r="P10" s="9">
         <v>42</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="9">
         <v>2.7536</v>
       </c>
       <c r="R10" s="5" t="inlineStr">
@@ -1598,7 +1627,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S10" s="9">
+      <c r="S10" s="10">
         <v>67</v>
       </c>
       <c r="U10" s="5" t="inlineStr">
@@ -1606,12 +1635,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr">
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1666,22 +1695,22 @@
       <c r="K11" s="9">
         <v>10.0584</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>12.5</v>
       </c>
       <c r="M11" s="9">
         <v>186</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="9">
         <v>0.08</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="10">
         <v>32</v>
       </c>
       <c r="P11" s="9">
         <v>75</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="9">
         <v>2.0355</v>
       </c>
       <c r="R11" s="5" t="inlineStr">
@@ -1689,7 +1718,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S11" s="9">
+      <c r="S11" s="10">
         <v>67</v>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -1697,12 +1726,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr">
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1757,22 +1786,22 @@
       <c r="K12" s="9">
         <v>10.0584</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>16.3999996185303</v>
       </c>
       <c r="M12" s="9">
         <v>269</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <v>0.116266663217221</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="10">
         <v>72</v>
       </c>
       <c r="P12" s="9">
         <v>14</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="9">
         <v>2.6288</v>
       </c>
       <c r="R12" s="5" t="inlineStr">
@@ -1780,7 +1809,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="10">
         <v>69</v>
       </c>
       <c r="U12" s="5" t="inlineStr">
@@ -1788,17 +1817,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" s="11">
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" s="12">
         <v>0</v>
       </c>
       <c r="Z12" s="5" t="inlineStr">
@@ -1851,19 +1880,19 @@
       <c r="K13" s="9">
         <v>14.0208</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <v>20.5</v>
       </c>
       <c r="M13" s="9">
         <v>7824</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="10">
         <v>40</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="9">
         <v>0.4925</v>
       </c>
       <c r="R13" s="5" t="inlineStr">
@@ -1871,7 +1900,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S13" s="9">
+      <c r="S13" s="10">
         <v>41</v>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -1879,17 +1908,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" s="11">
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" s="12">
         <v>0</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
@@ -1942,19 +1971,19 @@
       <c r="K14" s="9">
         <v>14.0208</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>20.5</v>
       </c>
       <c r="M14" s="9">
         <v>7824</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="10">
         <v>40</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <v>0.4203</v>
       </c>
       <c r="R14" s="5" t="inlineStr">
@@ -1962,7 +1991,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S14" s="9">
+      <c r="S14" s="10">
         <v>39</v>
       </c>
       <c r="U14" s="5" t="inlineStr">
@@ -1970,17 +1999,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" s="11">
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" s="12">
         <v>0</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
@@ -2033,19 +2062,19 @@
       <c r="K15" s="9">
         <v>5.4864</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="9">
         <v>21.3999996185303</v>
       </c>
       <c r="M15" s="9">
         <v>11579</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <v>6.57823246724982</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <v>22</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q15" s="9">
         <v>0.4307</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
@@ -2053,7 +2082,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="10">
         <v>40</v>
       </c>
       <c r="U15" s="5" t="inlineStr">
@@ -2061,17 +2090,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" s="11">
+      <c r="V15" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" s="12">
         <v>0</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
@@ -2124,19 +2153,19 @@
       <c r="K16" s="9">
         <v>4.572</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="9">
         <v>21.3999996185303</v>
       </c>
       <c r="M16" s="9">
         <v>7675</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>4.22113673098982</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <v>30</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="Q16" s="9">
         <v>0.2255</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
@@ -2144,7 +2173,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="10">
         <v>32</v>
       </c>
       <c r="U16" s="5" t="inlineStr">
@@ -2152,17 +2181,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" s="11">
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" s="12">
         <v>0</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
@@ -2215,19 +2244,19 @@
       <c r="K17" s="9">
         <v>9.144</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>19.2000007629395</v>
       </c>
       <c r="M17" s="9">
         <v>1466</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>0.714149189200495</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>27</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="9">
         <v>0.1861</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
@@ -2235,7 +2264,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="10">
         <v>31</v>
       </c>
       <c r="U17" s="5" t="inlineStr">
@@ -2243,17 +2272,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X17" s="11">
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" s="12">
         <v>0</v>
       </c>
       <c r="Z17" s="5" t="inlineStr">
@@ -2306,19 +2335,19 @@
       <c r="K18" s="9">
         <v>11.2776</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>21</v>
       </c>
       <c r="M18" s="9">
         <v>408</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="10">
         <v>28</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="9">
         <v>0.1458</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
@@ -2326,7 +2355,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S18" s="9">
+      <c r="S18" s="10">
         <v>28</v>
       </c>
       <c r="U18" s="5" t="inlineStr">
@@ -2334,17 +2363,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X18" s="11">
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X18" s="12">
         <v>0</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
@@ -2397,19 +2426,19 @@
       <c r="K19" s="9">
         <v>11.2776</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>21</v>
       </c>
       <c r="M19" s="9">
         <v>408</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="10">
         <v>28</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="9">
         <v>0.2121</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
@@ -2417,7 +2446,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S19" s="9">
+      <c r="S19" s="10">
         <v>32</v>
       </c>
       <c r="U19" s="5" t="inlineStr">
@@ -2425,17 +2454,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X19" s="11">
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" s="12">
         <v>0</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
@@ -2488,22 +2517,22 @@
       <c r="K20" s="9">
         <v>15.24</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>19.7999992370605</v>
       </c>
       <c r="M20" s="9">
         <v>1504</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="10">
         <v>44</v>
       </c>
       <c r="P20" s="9">
         <v>21.2000007629395</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q20" s="9">
         <v>0.3353</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
@@ -2511,7 +2540,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S20" s="9">
+      <c r="S20" s="10">
         <v>39</v>
       </c>
       <c r="U20" s="5" t="inlineStr">
@@ -2519,17 +2548,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X20" s="11">
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X20" s="12">
         <v>0</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
@@ -2582,22 +2611,22 @@
       <c r="K21" s="9">
         <v>10.3632</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>17.2</v>
       </c>
       <c r="M21" s="9">
         <v>1301</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="9">
         <v>0.628411617</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="10">
         <v>20</v>
       </c>
       <c r="P21" s="9">
         <v>62</v>
       </c>
-      <c r="Q21" s="10">
+      <c r="Q21" s="9">
         <v>2.7507</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
@@ -2605,7 +2634,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S21" s="9">
+      <c r="S21" s="10">
         <v>69</v>
       </c>
       <c r="U21" s="5" t="inlineStr">
@@ -2613,17 +2642,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X21" s="11">
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" s="12">
         <v>0</v>
       </c>
       <c r="Z21" s="5" t="inlineStr">
@@ -2676,22 +2705,22 @@
       <c r="K22" s="9">
         <v>2.7432</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="9">
         <v>17.1</v>
       </c>
       <c r="M22" s="9">
         <v>4263</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="9">
         <v>2.243137285</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="10">
         <v>27</v>
       </c>
       <c r="P22" s="9">
         <v>73</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="9">
         <v>1.7094</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
@@ -2699,7 +2728,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S22" s="9">
+      <c r="S22" s="10">
         <v>63</v>
       </c>
       <c r="U22" s="5" t="inlineStr">
@@ -2707,17 +2736,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X22" s="11">
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X22" s="12">
         <v>0</v>
       </c>
       <c r="Z22" s="5" t="inlineStr">
@@ -2770,22 +2799,22 @@
       <c r="K23" s="9">
         <v>11.5824</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="9">
         <v>17.9</v>
       </c>
       <c r="M23" s="9">
         <v>1538</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="9">
         <v>0.751786255</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="10">
         <v>17</v>
       </c>
       <c r="P23" s="9">
         <v>88</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="9">
         <v>2.0334</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
@@ -2793,7 +2822,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S23" s="9">
+      <c r="S23" s="10">
         <v>71</v>
       </c>
       <c r="U23" s="5" t="inlineStr">
@@ -2801,17 +2830,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X23" s="11">
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X23" s="12">
         <v>0</v>
       </c>
       <c r="Z23" s="5" t="inlineStr">
@@ -2864,22 +2893,22 @@
       <c r="K24" s="9">
         <v>15.24</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="9">
         <v>19.7999992370605</v>
       </c>
       <c r="M24" s="9">
         <v>1504</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="10">
         <v>44</v>
       </c>
       <c r="P24" s="9">
         <v>21.2000007629395</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="9">
         <v>0.1956</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
@@ -2887,7 +2916,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S24" s="9">
+      <c r="S24" s="10">
         <v>31</v>
       </c>
       <c r="U24" s="5" t="inlineStr">
@@ -2895,17 +2924,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X24" s="11">
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" s="12">
         <v>0</v>
       </c>
       <c r="Z24" s="5" t="inlineStr">
@@ -2958,19 +2987,19 @@
       <c r="K25" s="9">
         <v>11.2776</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="9">
         <v>21.1000003814697</v>
       </c>
       <c r="M25" s="9">
         <v>169</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="9">
         <v>7.07014200626035E-02</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="10">
         <v>43</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="Q25" s="9">
         <v>0.1009</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
@@ -2978,7 +3007,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="10">
         <v>23</v>
       </c>
       <c r="U25" s="5" t="inlineStr">
@@ -2986,17 +3015,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X25" s="11">
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X25" s="12">
         <v>0</v>
       </c>
       <c r="Z25" s="5" t="inlineStr">
@@ -3049,19 +3078,19 @@
       <c r="K26" s="9">
         <v>3.048</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="9">
         <v>21</v>
       </c>
       <c r="M26" s="9">
         <v>11517</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="10">
         <v>19</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="Q26" s="9">
         <v>0.9534</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
@@ -3069,10 +3098,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S26" s="9">
+      <c r="S26" s="10">
         <v>53</v>
       </c>
-      <c r="T26" s="10">
+      <c r="T26" s="9">
         <v>0.00202</v>
       </c>
       <c r="U26" s="5" t="inlineStr">
@@ -3080,20 +3109,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X26" s="11">
+      <c r="V26" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X26" s="12">
         <v>1</v>
       </c>
-      <c r="Y26" s="11">
+      <c r="Y26" s="12">
         <v>1</v>
       </c>
       <c r="Z26" s="5" t="inlineStr">
@@ -3146,19 +3175,19 @@
       <c r="K27" s="9">
         <v>3.048</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="9">
         <v>21</v>
       </c>
       <c r="M27" s="9">
         <v>11517</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="10">
         <v>19</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="9">
         <v>0.7283</v>
       </c>
       <c r="R27" s="5" t="inlineStr">
@@ -3166,7 +3195,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S27" s="9">
+      <c r="S27" s="10">
         <v>47</v>
       </c>
       <c r="U27" s="5" t="inlineStr">
@@ -3174,17 +3203,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X27" s="11">
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X27" s="12">
         <v>0</v>
       </c>
       <c r="Z27" s="5" t="inlineStr">
@@ -3237,19 +3266,19 @@
       <c r="K28" s="9">
         <v>3.048</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="9">
         <v>21</v>
       </c>
       <c r="M28" s="9">
         <v>11517</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="10">
         <v>19</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q28" s="9">
         <v>0.691</v>
       </c>
       <c r="R28" s="5" t="inlineStr">
@@ -3257,7 +3286,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S28" s="9">
+      <c r="S28" s="10">
         <v>46</v>
       </c>
       <c r="U28" s="5" t="inlineStr">
@@ -3265,17 +3294,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X28" s="11">
+      <c r="V28" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X28" s="12">
         <v>0</v>
       </c>
       <c r="Z28" s="5" t="inlineStr">
@@ -3328,19 +3357,19 @@
       <c r="K29" s="9">
         <v>1.524</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M29" s="9">
         <v>15729</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="10">
         <v>18</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="9">
         <v>0.4999</v>
       </c>
       <c r="R29" s="5" t="inlineStr">
@@ -3348,7 +3377,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S29" s="9">
+      <c r="S29" s="10">
         <v>42</v>
       </c>
       <c r="U29" s="5" t="inlineStr">
@@ -3356,17 +3385,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X29" s="11">
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X29" s="12">
         <v>0</v>
       </c>
       <c r="Z29" s="5" t="inlineStr">
@@ -3419,19 +3448,19 @@
       <c r="K30" s="9">
         <v>1.524</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M30" s="9">
         <v>15729</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="10">
         <v>18</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="9">
         <v>0.503</v>
       </c>
       <c r="R30" s="5" t="inlineStr">
@@ -3439,7 +3468,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S30" s="9">
+      <c r="S30" s="10">
         <v>42</v>
       </c>
       <c r="U30" s="5" t="inlineStr">
@@ -3447,17 +3476,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X30" s="11">
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X30" s="12">
         <v>0</v>
       </c>
       <c r="Z30" s="5" t="inlineStr">
@@ -3510,19 +3539,19 @@
       <c r="K31" s="9">
         <v>1.524</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M31" s="9">
         <v>15729</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="10">
         <v>18</v>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q31" s="9">
         <v>0.5018</v>
       </c>
       <c r="R31" s="5" t="inlineStr">
@@ -3530,7 +3559,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S31" s="9">
+      <c r="S31" s="10">
         <v>43</v>
       </c>
       <c r="U31" s="5" t="inlineStr">
@@ -3538,17 +3567,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X31" s="11">
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X31" s="12">
         <v>0</v>
       </c>
       <c r="Z31" s="5" t="inlineStr">
@@ -3601,19 +3630,19 @@
       <c r="K32" s="9">
         <v>1.524</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M32" s="9">
         <v>15729</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O32" s="9">
+      <c r="O32" s="10">
         <v>18</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q32" s="9">
         <v>1.2122</v>
       </c>
       <c r="R32" s="5" t="inlineStr">
@@ -3621,7 +3650,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S32" s="9">
+      <c r="S32" s="10">
         <v>57</v>
       </c>
       <c r="U32" s="5" t="inlineStr">
@@ -3629,17 +3658,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X32" s="11">
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X32" s="12">
         <v>0</v>
       </c>
       <c r="Z32" s="5" t="inlineStr">
@@ -3692,19 +3721,19 @@
       <c r="K33" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="9">
         <v>19.8999996185303</v>
       </c>
       <c r="M33" s="9">
         <v>17766</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="10">
+      <c r="Q33" s="9">
         <v>0.6167</v>
       </c>
       <c r="R33" s="5" t="inlineStr">
@@ -3712,7 +3741,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S33" s="9">
+      <c r="S33" s="10">
         <v>45</v>
       </c>
       <c r="U33" s="5" t="inlineStr">
@@ -3720,17 +3749,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X33" s="11">
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X33" s="12">
         <v>0</v>
       </c>
       <c r="Z33" s="5" t="inlineStr">
@@ -3783,19 +3812,19 @@
       <c r="K34" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="9">
         <v>19.8999996185303</v>
       </c>
       <c r="M34" s="9">
         <v>17766</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="10">
         <v>10</v>
       </c>
-      <c r="Q34" s="10">
+      <c r="Q34" s="9">
         <v>0.2372</v>
       </c>
       <c r="R34" s="5" t="inlineStr">
@@ -3803,7 +3832,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S34" s="9">
+      <c r="S34" s="10">
         <v>34</v>
       </c>
       <c r="U34" s="5" t="inlineStr">
@@ -3811,17 +3840,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X34" s="11">
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X34" s="12">
         <v>0</v>
       </c>
       <c r="Z34" s="5" t="inlineStr">
@@ -3874,19 +3903,19 @@
       <c r="K35" s="9">
         <v>8.8392</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="9">
         <v>23.2000007629395</v>
       </c>
       <c r="M35" s="9">
         <v>333</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="9">
         <v>0.146101890125461</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="10">
         <v>63</v>
       </c>
-      <c r="Q35" s="10">
+      <c r="Q35" s="9">
         <v>0.4283</v>
       </c>
       <c r="R35" s="5" t="inlineStr">
@@ -3894,7 +3923,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S35" s="9">
+      <c r="S35" s="10">
         <v>42</v>
       </c>
       <c r="U35" s="5" t="inlineStr">
@@ -3902,17 +3931,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X35" s="11">
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X35" s="12">
         <v>0</v>
       </c>
       <c r="Z35" s="5" t="inlineStr">
@@ -3965,22 +3994,22 @@
       <c r="K36" s="9">
         <v>9.7536</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M36" s="9">
         <v>732</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="9">
         <v>0.339467723207604</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="10">
         <v>33</v>
       </c>
       <c r="P36" s="9">
         <v>33.7999992370605</v>
       </c>
-      <c r="Q36" s="10">
+      <c r="Q36" s="9">
         <v>0.3137</v>
       </c>
       <c r="R36" s="5" t="inlineStr">
@@ -3988,7 +4017,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S36" s="9">
+      <c r="S36" s="10">
         <v>37</v>
       </c>
       <c r="U36" s="5" t="inlineStr">
@@ -3996,17 +4025,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X36" s="11">
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X36" s="12">
         <v>0</v>
       </c>
       <c r="Z36" s="5" t="inlineStr">
@@ -4059,22 +4088,22 @@
       <c r="K37" s="9">
         <v>15.24</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="9">
         <v>20</v>
       </c>
       <c r="M37" s="9">
         <v>1930</v>
       </c>
-      <c r="N37" s="10">
+      <c r="N37" s="9">
         <v>0.958821325062239</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="10">
         <v>36</v>
       </c>
       <c r="P37" s="9">
         <v>31.6000003814697</v>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="9">
         <v>0.114</v>
       </c>
       <c r="R37" s="5" t="inlineStr">
@@ -4082,7 +4111,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S37" s="9">
+      <c r="S37" s="10">
         <v>29</v>
       </c>
       <c r="U37" s="5" t="inlineStr">
@@ -4090,17 +4119,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X37" s="11">
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X37" s="12">
         <v>0</v>
       </c>
       <c r="Z37" s="5" t="inlineStr">
@@ -4153,22 +4182,22 @@
       <c r="K38" s="9">
         <v>4.572</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="9">
         <v>19.8999996185303</v>
       </c>
       <c r="M38" s="9">
         <v>6550</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="9">
         <v>3.55899409093209</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="10">
         <v>30</v>
       </c>
       <c r="P38" s="9">
         <v>25.8999996185303</v>
       </c>
-      <c r="Q38" s="10">
+      <c r="Q38" s="9">
         <v>0.1645</v>
       </c>
       <c r="R38" s="5" t="inlineStr">
@@ -4176,7 +4205,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S38" s="9">
+      <c r="S38" s="10">
         <v>28</v>
       </c>
       <c r="U38" s="5" t="inlineStr">
@@ -4184,17 +4213,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X38" s="11">
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X38" s="12">
         <v>0</v>
       </c>
       <c r="Z38" s="5" t="inlineStr">
@@ -4247,22 +4276,22 @@
       <c r="K39" s="9">
         <v>10.3632</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="9">
         <v>14.3000001907349</v>
       </c>
       <c r="M39" s="9">
         <v>2329</v>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="9">
         <v>1.17275584161783</v>
       </c>
-      <c r="O39" s="9">
+      <c r="O39" s="10">
         <v>49.0000009536743</v>
       </c>
       <c r="P39" s="9">
         <v>17.8999996185303</v>
       </c>
-      <c r="Q39" s="10">
+      <c r="Q39" s="9">
         <v>1.6951</v>
       </c>
       <c r="R39" s="5" t="inlineStr">
@@ -4270,7 +4299,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S39" s="9">
+      <c r="S39" s="10">
         <v>63</v>
       </c>
       <c r="U39" s="5" t="inlineStr">
@@ -4278,17 +4307,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X39" s="11">
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X39" s="12">
         <v>0</v>
       </c>
       <c r="Z39" s="5" t="inlineStr">
@@ -4341,22 +4370,22 @@
       <c r="K40" s="9">
         <v>10.0584</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="9">
         <v>13.6999998092651</v>
       </c>
       <c r="M40" s="9">
         <v>211</v>
       </c>
-      <c r="N40" s="10">
+      <c r="N40" s="9">
         <v>8.96570505211038E-02</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="10">
         <v>38</v>
       </c>
       <c r="P40" s="9">
         <v>30</v>
       </c>
-      <c r="Q40" s="10">
+      <c r="Q40" s="9">
         <v>2.1</v>
       </c>
       <c r="R40" s="5" t="inlineStr">
@@ -4364,7 +4393,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S40" s="9">
+      <c r="S40" s="10">
         <v>69</v>
       </c>
       <c r="U40" s="5" t="inlineStr">
@@ -4372,17 +4401,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X40" s="11">
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X40" s="12">
         <v>0</v>
       </c>
       <c r="Z40" s="5" t="inlineStr">
@@ -4435,22 +4464,22 @@
       <c r="K41" s="9">
         <v>8.8392</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="9">
         <v>21.3999996185303</v>
       </c>
       <c r="M41" s="9">
         <v>1544</v>
       </c>
-      <c r="N41" s="10">
+      <c r="N41" s="9">
         <v>0.754928529738625</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="10">
         <v>48</v>
       </c>
       <c r="P41" s="9">
         <v>20.7999992370605</v>
       </c>
-      <c r="Q41" s="10">
+      <c r="Q41" s="9">
         <v>0.0909</v>
       </c>
       <c r="R41" s="5" t="inlineStr">
@@ -4458,7 +4487,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S41" s="9">
+      <c r="S41" s="10">
         <v>24</v>
       </c>
       <c r="U41" s="5" t="inlineStr">
@@ -4466,17 +4495,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X41" s="11">
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X41" s="12">
         <v>0</v>
       </c>
       <c r="Z41" s="5" t="inlineStr">
@@ -4529,22 +4558,22 @@
       <c r="K42" s="9">
         <v>7.62</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="9">
         <v>21.5</v>
       </c>
       <c r="M42" s="9">
         <v>3310</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="10">
         <v>41</v>
       </c>
       <c r="P42" s="9">
         <v>24.6000003814697</v>
       </c>
-      <c r="Q42" s="10">
+      <c r="Q42" s="9">
         <v>0.218</v>
       </c>
       <c r="R42" s="5" t="inlineStr">
@@ -4552,7 +4581,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S42" s="9">
+      <c r="S42" s="10">
         <v>32</v>
       </c>
       <c r="U42" s="5" t="inlineStr">
@@ -4560,17 +4589,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X42" s="11">
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X42" s="12">
         <v>0</v>
       </c>
       <c r="Z42" s="5" t="inlineStr">
@@ -4623,22 +4652,22 @@
       <c r="K43" s="9">
         <v>7.62</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="9">
         <v>21.5</v>
       </c>
       <c r="M43" s="9">
         <v>3310</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="10">
         <v>41</v>
       </c>
       <c r="P43" s="9">
         <v>24.6000003814697</v>
       </c>
-      <c r="Q43" s="10">
+      <c r="Q43" s="9">
         <v>0.1141</v>
       </c>
       <c r="R43" s="5" t="inlineStr">
@@ -4646,7 +4675,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S43" s="9">
+      <c r="S43" s="10">
         <v>26</v>
       </c>
       <c r="U43" s="5" t="inlineStr">
@@ -4654,17 +4683,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X43" s="11">
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X43" s="12">
         <v>0</v>
       </c>
       <c r="Z43" s="5" t="inlineStr">
@@ -4717,22 +4746,22 @@
       <c r="K44" s="9">
         <v>8.8392</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="9">
         <v>20.8999996185303</v>
       </c>
       <c r="M44" s="9">
         <v>4215</v>
       </c>
-      <c r="N44" s="10">
+      <c r="N44" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O44" s="9">
+      <c r="O44" s="10">
         <v>36</v>
       </c>
       <c r="P44" s="9">
         <v>46.5999984741211</v>
       </c>
-      <c r="Q44" s="10">
+      <c r="Q44" s="9">
         <v>0.1468</v>
       </c>
       <c r="R44" s="5" t="inlineStr">
@@ -4740,7 +4769,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S44" s="9">
+      <c r="S44" s="10">
         <v>28</v>
       </c>
       <c r="U44" s="5" t="inlineStr">
@@ -4748,17 +4777,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X44" s="11">
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X44" s="12">
         <v>0</v>
       </c>
       <c r="Z44" s="5" t="inlineStr">
@@ -4811,22 +4840,22 @@
       <c r="K45" s="9">
         <v>8.8392</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="9">
         <v>20.8999996185303</v>
       </c>
       <c r="M45" s="9">
         <v>4215</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O45" s="10">
         <v>36</v>
       </c>
       <c r="P45" s="9">
         <v>46.5999984741211</v>
       </c>
-      <c r="Q45" s="10">
+      <c r="Q45" s="9">
         <v>0.1133</v>
       </c>
       <c r="R45" s="5" t="inlineStr">
@@ -4834,7 +4863,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S45" s="9">
+      <c r="S45" s="10">
         <v>26</v>
       </c>
       <c r="U45" s="5" t="inlineStr">
@@ -4842,17 +4871,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X45" s="11">
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X45" s="12">
         <v>0</v>
       </c>
       <c r="Z45" s="5" t="inlineStr">
@@ -4905,22 +4934,22 @@
       <c r="K46" s="9">
         <v>8.8392</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46" s="9">
         <v>20.8999996185303</v>
       </c>
       <c r="M46" s="9">
         <v>4215</v>
       </c>
-      <c r="N46" s="10">
+      <c r="N46" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O46" s="10">
         <v>36</v>
       </c>
       <c r="P46" s="9">
         <v>46.5999984741211</v>
       </c>
-      <c r="Q46" s="10">
+      <c r="Q46" s="9">
         <v>0.1751</v>
       </c>
       <c r="R46" s="5" t="inlineStr">
@@ -4928,7 +4957,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S46" s="9">
+      <c r="S46" s="10">
         <v>28</v>
       </c>
       <c r="U46" s="5" t="inlineStr">
@@ -4936,17 +4965,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X46" s="11">
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X46" s="12">
         <v>0</v>
       </c>
       <c r="Z46" s="5" t="inlineStr">
@@ -4999,22 +5028,22 @@
       <c r="K47" s="9">
         <v>7.3152</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M47" s="9">
         <v>3398</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O47" s="10">
         <v>37</v>
       </c>
       <c r="P47" s="9">
         <v>29.6000003814697</v>
       </c>
-      <c r="Q47" s="10">
+      <c r="Q47" s="9">
         <v>0.1101</v>
       </c>
       <c r="R47" s="5" t="inlineStr">
@@ -5022,7 +5051,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S47" s="9">
+      <c r="S47" s="10">
         <v>26</v>
       </c>
       <c r="U47" s="5" t="inlineStr">
@@ -5030,17 +5059,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X47" s="11">
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X47" s="12">
         <v>0</v>
       </c>
       <c r="Z47" s="5" t="inlineStr">
@@ -5093,22 +5122,22 @@
       <c r="K48" s="9">
         <v>7.3152</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48" s="9">
         <v>20.3999996185303</v>
       </c>
       <c r="M48" s="9">
         <v>3398</v>
       </c>
-      <c r="N48" s="10">
+      <c r="N48" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O48" s="9">
+      <c r="O48" s="10">
         <v>37</v>
       </c>
       <c r="P48" s="9">
         <v>29.6000003814697</v>
       </c>
-      <c r="Q48" s="10">
+      <c r="Q48" s="9">
         <v>0.2521</v>
       </c>
       <c r="R48" s="5" t="inlineStr">
@@ -5116,7 +5145,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S48" s="9">
+      <c r="S48" s="10">
         <v>35</v>
       </c>
       <c r="U48" s="5" t="inlineStr">
@@ -5124,17 +5153,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X48" s="11">
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X48" s="12">
         <v>0</v>
       </c>
       <c r="Z48" s="5" t="inlineStr">
@@ -5187,22 +5216,22 @@
       <c r="K49" s="9">
         <v>10.3632</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49" s="9">
         <v>21.3999996185303</v>
       </c>
       <c r="M49" s="9">
         <v>424</v>
       </c>
-      <c r="N49" s="10">
+      <c r="N49" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O49" s="9">
+      <c r="O49" s="10">
         <v>39</v>
       </c>
       <c r="P49" s="9">
         <v>34.7999992370605</v>
       </c>
-      <c r="Q49" s="10">
+      <c r="Q49" s="9">
         <v>0.1797</v>
       </c>
       <c r="R49" s="5" t="inlineStr">
@@ -5210,7 +5239,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S49" s="9">
+      <c r="S49" s="10">
         <v>31</v>
       </c>
       <c r="U49" s="5" t="inlineStr">
@@ -5218,17 +5247,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X49" s="11">
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X49" s="12">
         <v>0</v>
       </c>
       <c r="Z49" s="5" t="inlineStr">
@@ -5281,22 +5310,22 @@
       <c r="K50" s="9">
         <v>10.3632</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="9">
         <v>21.3999996185303</v>
       </c>
       <c r="M50" s="9">
         <v>424</v>
       </c>
-      <c r="N50" s="10">
+      <c r="N50" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O50" s="9">
+      <c r="O50" s="10">
         <v>39</v>
       </c>
       <c r="P50" s="9">
         <v>34.7999992370605</v>
       </c>
-      <c r="Q50" s="10">
+      <c r="Q50" s="9">
         <v>0.121</v>
       </c>
       <c r="R50" s="5" t="inlineStr">
@@ -5304,7 +5333,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S50" s="9">
+      <c r="S50" s="10">
         <v>27</v>
       </c>
       <c r="U50" s="5" t="inlineStr">
@@ -5312,17 +5341,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X50" s="11">
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X50" s="12">
         <v>0</v>
       </c>
       <c r="Z50" s="5" t="inlineStr">
@@ -5375,22 +5404,22 @@
       <c r="K51" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="9">
         <v>21.1000003814697</v>
       </c>
       <c r="M51" s="9">
         <v>18512</v>
       </c>
-      <c r="N51" s="10">
+      <c r="N51" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O51" s="9">
+      <c r="O51" s="10">
         <v>21</v>
       </c>
       <c r="P51" s="9">
         <v>266</v>
       </c>
-      <c r="Q51" s="10">
+      <c r="Q51" s="9">
         <v>0.4734</v>
       </c>
       <c r="R51" s="5" t="inlineStr">
@@ -5398,7 +5427,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S51" s="9">
+      <c r="S51" s="10">
         <v>42</v>
       </c>
       <c r="U51" s="5" t="inlineStr">
@@ -5406,17 +5435,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X51" s="11">
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X51" s="12">
         <v>0</v>
       </c>
       <c r="Z51" s="5" t="inlineStr">
@@ -5469,22 +5498,22 @@
       <c r="K52" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="9">
         <v>21.1000003814697</v>
       </c>
       <c r="M52" s="9">
         <v>18512</v>
       </c>
-      <c r="N52" s="10">
+      <c r="N52" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O52" s="9">
+      <c r="O52" s="10">
         <v>21</v>
       </c>
       <c r="P52" s="9">
         <v>266</v>
       </c>
-      <c r="Q52" s="10">
+      <c r="Q52" s="9">
         <v>0.9917</v>
       </c>
       <c r="R52" s="5" t="inlineStr">
@@ -5492,7 +5521,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S52" s="9">
+      <c r="S52" s="10">
         <v>53</v>
       </c>
       <c r="U52" s="5" t="inlineStr">
@@ -5500,17 +5529,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X52" s="11">
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X52" s="12">
         <v>0</v>
       </c>
       <c r="Z52" s="5" t="inlineStr">
@@ -5563,22 +5592,22 @@
       <c r="K53" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53" s="9">
         <v>21.1000003814697</v>
       </c>
       <c r="M53" s="9">
         <v>18512</v>
       </c>
-      <c r="N53" s="10">
+      <c r="N53" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O53" s="9">
+      <c r="O53" s="10">
         <v>21</v>
       </c>
       <c r="P53" s="9">
         <v>266</v>
       </c>
-      <c r="Q53" s="10">
+      <c r="Q53" s="9">
         <v>1.4803</v>
       </c>
       <c r="R53" s="5" t="inlineStr">
@@ -5586,7 +5615,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S53" s="9">
+      <c r="S53" s="10">
         <v>61</v>
       </c>
       <c r="U53" s="5" t="inlineStr">
@@ -5594,17 +5623,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X53" s="11">
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X53" s="12">
         <v>0</v>
       </c>
       <c r="Z53" s="5" t="inlineStr">
@@ -5657,22 +5686,22 @@
       <c r="K54" s="9">
         <v>1.2192</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="9">
         <v>21.1000003814697</v>
       </c>
       <c r="M54" s="9">
         <v>18512</v>
       </c>
-      <c r="N54" s="10">
+      <c r="N54" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O54" s="9">
+      <c r="O54" s="10">
         <v>21</v>
       </c>
       <c r="P54" s="9">
         <v>266</v>
       </c>
-      <c r="Q54" s="10">
+      <c r="Q54" s="9">
         <v>0.6141</v>
       </c>
       <c r="R54" s="5" t="inlineStr">
@@ -5680,7 +5709,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S54" s="9">
+      <c r="S54" s="10">
         <v>46</v>
       </c>
       <c r="U54" s="5" t="inlineStr">
@@ -5688,17 +5717,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X54" s="11">
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X54" s="12">
         <v>0</v>
       </c>
       <c r="Z54" s="5" t="inlineStr">
@@ -5751,22 +5780,22 @@
       <c r="K55" s="9">
         <v>10.3632</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="9">
         <v>11.5</v>
       </c>
       <c r="M55" s="9">
         <v>165</v>
       </c>
-      <c r="N55" s="10">
+      <c r="N55" s="9">
         <v>0.07</v>
       </c>
-      <c r="O55" s="9">
+      <c r="O55" s="10">
         <v>12</v>
       </c>
       <c r="P55" s="9">
         <v>197</v>
       </c>
-      <c r="Q55" s="10">
+      <c r="Q55" s="9">
         <v>1.1768</v>
       </c>
       <c r="R55" s="5" t="inlineStr">
@@ -5774,7 +5803,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S55" s="9">
+      <c r="S55" s="10">
         <v>58</v>
       </c>
       <c r="U55" s="5" t="inlineStr">
@@ -5782,17 +5811,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X55" s="11">
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X55" s="12">
         <v>0</v>
       </c>
       <c r="Z55" s="5" t="inlineStr">
@@ -5803,7 +5832,7 @@
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -5826,12 +5855,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>0036</t>
+          <t>0033</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -5840,53 +5869,50 @@
         </is>
       </c>
       <c r="J56" s="8">
-        <v>0.468055555555556</v>
-      </c>
-      <c r="K56" s="9">
-        <v>7.3152</v>
-      </c>
-      <c r="L56" s="10">
-        <v>22.6</v>
+        <v>0.395833333333333</v>
+      </c>
+      <c r="L56" s="9">
+        <v>21.8</v>
       </c>
       <c r="M56" s="9">
-        <v>1214</v>
-      </c>
-      <c r="N56" s="10">
-        <v>0.58</v>
-      </c>
-      <c r="O56" s="9">
-        <v>0.66</v>
+        <v>1245</v>
+      </c>
+      <c r="N56" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="O56" s="10">
+        <v>0.6</v>
       </c>
       <c r="P56" s="9">
-        <v>13.2</v>
-      </c>
-      <c r="Q56" s="10">
-        <v>0.3505</v>
+        <v>15.6</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>0.6815</v>
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S56" s="9">
-        <v>38</v>
+      <c r="S56" s="10">
+        <v>44</v>
       </c>
       <c r="U56" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V56" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X56" s="11">
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X56" s="12">
         <v>0</v>
       </c>
       <c r="Z56" s="5" t="inlineStr">
@@ -5897,7 +5923,7 @@
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="4">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -5920,12 +5946,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>0036</t>
+          <t>0035</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -5934,50 +5960,50 @@
         </is>
       </c>
       <c r="J57" s="8">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="L57" s="10">
-        <v>22</v>
+        <v>0.395833333333333</v>
+      </c>
+      <c r="L57" s="9">
+        <v>21.8</v>
       </c>
       <c r="M57" s="9">
-        <v>4398</v>
-      </c>
-      <c r="N57" s="10">
-        <v>2.32</v>
-      </c>
-      <c r="O57" s="9">
-        <v>0.59</v>
+        <v>1245</v>
+      </c>
+      <c r="N57" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="O57" s="10">
+        <v>0.6</v>
       </c>
       <c r="P57" s="9">
-        <v>17.9</v>
-      </c>
-      <c r="Q57" s="10">
-        <v>0.3505</v>
+        <v>15.6</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>1.0364</v>
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S57" s="9">
-        <v>38</v>
+      <c r="S57" s="10">
+        <v>52</v>
       </c>
       <c r="U57" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X57" s="11">
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X57" s="12">
         <v>0</v>
       </c>
       <c r="Z57" s="5" t="inlineStr">
@@ -5997,7 +6023,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>MWTCC</t>
+          <t>FMWTCC</t>
         </is>
       </c>
       <c r="D58" s="6">
@@ -6025,27 +6051,24 @@
         </is>
       </c>
       <c r="J58" s="8">
-        <v>0.525694444444444</v>
-      </c>
-      <c r="K58" s="9">
-        <v>9.144</v>
-      </c>
-      <c r="L58" s="10">
-        <v>23.4</v>
+        <v>0.572916666666667</v>
+      </c>
+      <c r="L58" s="9">
+        <v>22</v>
       </c>
       <c r="M58" s="9">
-        <v>2071</v>
-      </c>
-      <c r="N58" s="10">
-        <v>1.03</v>
-      </c>
-      <c r="O58" s="9">
-        <v>0.54</v>
+        <v>4398</v>
+      </c>
+      <c r="N58" s="9">
+        <v>2.32</v>
+      </c>
+      <c r="O58" s="10">
+        <v>0.59</v>
       </c>
       <c r="P58" s="9">
-        <v>16.7</v>
-      </c>
-      <c r="Q58" s="10">
+        <v>17.9</v>
+      </c>
+      <c r="Q58" s="9">
         <v>0.3505</v>
       </c>
       <c r="R58" s="5" t="inlineStr">
@@ -6053,7 +6076,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S58" s="9">
+      <c r="S58" s="10">
         <v>38</v>
       </c>
       <c r="U58" s="5" t="inlineStr">
@@ -6061,17 +6084,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V58" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W58" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X58" s="11">
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X58" s="12">
         <v>0</v>
       </c>
       <c r="Z58" s="5" t="inlineStr">
@@ -6119,27 +6142,27 @@
         </is>
       </c>
       <c r="J59" s="8">
-        <v>0.552777777777778</v>
+        <v>0.468055555555556</v>
       </c>
       <c r="K59" s="9">
-        <v>9.7536</v>
-      </c>
-      <c r="L59" s="10">
-        <v>23.4</v>
+        <v>7.3152</v>
+      </c>
+      <c r="L59" s="9">
+        <v>22.6</v>
       </c>
       <c r="M59" s="9">
-        <v>3175</v>
-      </c>
-      <c r="N59" s="10">
-        <v>1.63</v>
-      </c>
-      <c r="O59" s="9">
-        <v>0.57</v>
+        <v>1214</v>
+      </c>
+      <c r="N59" s="9">
+        <v>0.58</v>
+      </c>
+      <c r="O59" s="10">
+        <v>0.66</v>
       </c>
       <c r="P59" s="9">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="10">
+        <v>13.2</v>
+      </c>
+      <c r="Q59" s="9">
         <v>0.3505</v>
       </c>
       <c r="R59" s="5" t="inlineStr">
@@ -6147,7 +6170,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S59" s="9">
+      <c r="S59" s="10">
         <v>38</v>
       </c>
       <c r="U59" s="5" t="inlineStr">
@@ -6155,17 +6178,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V59" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W59" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X59" s="11">
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X59" s="12">
         <v>0</v>
       </c>
       <c r="Z59" s="5" t="inlineStr">
@@ -6176,7 +6199,7 @@
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4">
-        <v>1934</v>
+        <v>1928</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -6185,7 +6208,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D60" s="6">
@@ -6204,7 +6227,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>0049</t>
+          <t>0036</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -6213,53 +6236,53 @@
         </is>
       </c>
       <c r="J60" s="8">
-        <v>0.468055555555556</v>
+        <v>0.525694444444444</v>
       </c>
       <c r="K60" s="9">
-        <v>7.3152</v>
-      </c>
-      <c r="L60" s="10">
-        <v>22.6</v>
+        <v>9.144</v>
+      </c>
+      <c r="L60" s="9">
+        <v>23.4</v>
       </c>
       <c r="M60" s="9">
-        <v>1214</v>
-      </c>
-      <c r="N60" s="10">
-        <v>0.58</v>
-      </c>
-      <c r="O60" s="9">
-        <v>0.66</v>
+        <v>2071</v>
+      </c>
+      <c r="N60" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="O60" s="10">
+        <v>0.54</v>
       </c>
       <c r="P60" s="9">
-        <v>13.2</v>
-      </c>
-      <c r="Q60" s="10">
-        <v>1.0031</v>
+        <v>16.7</v>
+      </c>
+      <c r="Q60" s="9">
+        <v>0.3505</v>
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S60" s="9">
-        <v>52</v>
+      <c r="S60" s="10">
+        <v>38</v>
       </c>
       <c r="U60" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V60" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W60" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X60" s="11">
+      <c r="V60" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X60" s="12">
         <v>0</v>
       </c>
       <c r="Z60" s="5" t="inlineStr">
@@ -6270,7 +6293,7 @@
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4">
-        <v>1934</v>
+        <v>1928</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -6279,7 +6302,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D61" s="6">
@@ -6298,7 +6321,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>0049</t>
+          <t>0036</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -6307,50 +6330,53 @@
         </is>
       </c>
       <c r="J61" s="8">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="L61" s="10">
-        <v>22</v>
+        <v>0.552777777777778</v>
+      </c>
+      <c r="K61" s="9">
+        <v>9.7536</v>
+      </c>
+      <c r="L61" s="9">
+        <v>23.4</v>
       </c>
       <c r="M61" s="9">
-        <v>4398</v>
-      </c>
-      <c r="N61" s="10">
-        <v>2.32</v>
-      </c>
-      <c r="O61" s="9">
-        <v>0.59</v>
+        <v>3175</v>
+      </c>
+      <c r="N61" s="9">
+        <v>1.63</v>
+      </c>
+      <c r="O61" s="10">
+        <v>0.57</v>
       </c>
       <c r="P61" s="9">
-        <v>17.9</v>
-      </c>
-      <c r="Q61" s="10">
-        <v>1.0031</v>
+        <v>20</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>0.3505</v>
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S61" s="9">
-        <v>52</v>
+      <c r="S61" s="10">
+        <v>38</v>
       </c>
       <c r="U61" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W61" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X61" s="11">
+      <c r="V61" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X61" s="12">
         <v>0</v>
       </c>
       <c r="Z61" s="5" t="inlineStr">
@@ -6370,7 +6396,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>MWTCC</t>
+          <t>FMWTCC</t>
         </is>
       </c>
       <c r="D62" s="6">
@@ -6398,27 +6424,24 @@
         </is>
       </c>
       <c r="J62" s="8">
-        <v>0.525694444444444</v>
-      </c>
-      <c r="K62" s="9">
-        <v>9.144</v>
-      </c>
-      <c r="L62" s="10">
-        <v>23.4</v>
+        <v>0.572916666666667</v>
+      </c>
+      <c r="L62" s="9">
+        <v>22</v>
       </c>
       <c r="M62" s="9">
-        <v>2071</v>
-      </c>
-      <c r="N62" s="10">
-        <v>1.03</v>
-      </c>
-      <c r="O62" s="9">
-        <v>0.54</v>
+        <v>4398</v>
+      </c>
+      <c r="N62" s="9">
+        <v>2.32</v>
+      </c>
+      <c r="O62" s="10">
+        <v>0.59</v>
       </c>
       <c r="P62" s="9">
-        <v>16.7</v>
-      </c>
-      <c r="Q62" s="10">
+        <v>17.9</v>
+      </c>
+      <c r="Q62" s="9">
         <v>1.0031</v>
       </c>
       <c r="R62" s="5" t="inlineStr">
@@ -6426,7 +6449,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S62" s="9">
+      <c r="S62" s="10">
         <v>52</v>
       </c>
       <c r="U62" s="5" t="inlineStr">
@@ -6434,17 +6457,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V62" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W62" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X62" s="11">
+      <c r="V62" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X62" s="12">
         <v>0</v>
       </c>
       <c r="Z62" s="5" t="inlineStr">
@@ -6492,27 +6515,27 @@
         </is>
       </c>
       <c r="J63" s="8">
-        <v>0.552777777777778</v>
+        <v>0.468055555555556</v>
       </c>
       <c r="K63" s="9">
-        <v>9.7536</v>
-      </c>
-      <c r="L63" s="10">
-        <v>23.4</v>
+        <v>7.3152</v>
+      </c>
+      <c r="L63" s="9">
+        <v>22.6</v>
       </c>
       <c r="M63" s="9">
-        <v>3175</v>
-      </c>
-      <c r="N63" s="10">
-        <v>1.63</v>
-      </c>
-      <c r="O63" s="9">
-        <v>0.57</v>
+        <v>1214</v>
+      </c>
+      <c r="N63" s="9">
+        <v>0.58</v>
+      </c>
+      <c r="O63" s="10">
+        <v>0.66</v>
       </c>
       <c r="P63" s="9">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="10">
+        <v>13.2</v>
+      </c>
+      <c r="Q63" s="9">
         <v>1.0031</v>
       </c>
       <c r="R63" s="5" t="inlineStr">
@@ -6520,7 +6543,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S63" s="9">
+      <c r="S63" s="10">
         <v>52</v>
       </c>
       <c r="U63" s="5" t="inlineStr">
@@ -6528,17 +6551,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V63" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W63" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X63" s="11">
+      <c r="V63" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X63" s="12">
         <v>0</v>
       </c>
       <c r="Z63" s="5" t="inlineStr">
@@ -6549,7 +6572,7 @@
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4">
-        <v>1974</v>
+        <v>1934</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -6558,7 +6581,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D64" s="6">
@@ -6572,12 +6595,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>0177</t>
+          <t>0049</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -6586,53 +6609,53 @@
         </is>
       </c>
       <c r="J64" s="8">
-        <v>0.667361111111111</v>
+        <v>0.525694444444444</v>
       </c>
       <c r="K64" s="9">
         <v>9.144</v>
       </c>
-      <c r="L64" s="10">
-        <v>23.3</v>
+      <c r="L64" s="9">
+        <v>23.4</v>
       </c>
       <c r="M64" s="9">
-        <v>541</v>
-      </c>
-      <c r="N64" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="O64" s="9">
-        <v>0.45</v>
+        <v>2071</v>
+      </c>
+      <c r="N64" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="O64" s="10">
+        <v>0.54</v>
       </c>
       <c r="P64" s="9">
-        <v>28.2</v>
-      </c>
-      <c r="Q64" s="10">
-        <v>0.7422</v>
+        <v>16.7</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>1.0031</v>
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S64" s="9">
-        <v>44</v>
+      <c r="S64" s="10">
+        <v>52</v>
       </c>
       <c r="U64" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V64" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W64" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X64" s="11">
+      <c r="V64" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X64" s="12">
         <v>0</v>
       </c>
       <c r="Z64" s="5" t="inlineStr">
@@ -6643,7 +6666,7 @@
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4">
-        <v>1991</v>
+        <v>1934</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -6652,7 +6675,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D65" s="6">
@@ -6666,12 +6689,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>0229</t>
+          <t>0049</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -6680,35 +6703,35 @@
         </is>
       </c>
       <c r="J65" s="8">
-        <v>0.667361111111111</v>
+        <v>0.552777777777778</v>
       </c>
       <c r="K65" s="9">
-        <v>9.144</v>
-      </c>
-      <c r="L65" s="10">
-        <v>23.3</v>
+        <v>9.7536</v>
+      </c>
+      <c r="L65" s="9">
+        <v>23.4</v>
       </c>
       <c r="M65" s="9">
-        <v>541</v>
-      </c>
-      <c r="N65" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="O65" s="9">
-        <v>0.45</v>
+        <v>3175</v>
+      </c>
+      <c r="N65" s="9">
+        <v>1.63</v>
+      </c>
+      <c r="O65" s="10">
+        <v>0.57</v>
       </c>
       <c r="P65" s="9">
-        <v>28.2</v>
-      </c>
-      <c r="Q65" s="10">
-        <v>1.1469</v>
+        <v>20</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>1.0031</v>
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S65" s="9">
+      <c r="S65" s="10">
         <v>52</v>
       </c>
       <c r="U65" s="5" t="inlineStr">
@@ -6716,17 +6739,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V65" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W65" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X65" s="11">
+      <c r="V65" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W65" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X65" s="12">
         <v>0</v>
       </c>
       <c r="Z65" s="5" t="inlineStr">
@@ -6737,7 +6760,7 @@
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4">
-        <v>2010</v>
+        <v>1974</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -6746,26 +6769,26 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D66" s="6">
         <v>2014</v>
       </c>
       <c r="E66" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F66" s="7">
-        <v>41907</v>
+        <v>41872</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>0266</t>
+          <t>0177</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -6774,53 +6797,53 @@
         </is>
       </c>
       <c r="J66" s="8">
-        <v>0.388888888888889</v>
+        <v>0.667361111111111</v>
       </c>
       <c r="K66" s="9">
         <v>9.144</v>
       </c>
-      <c r="L66" s="10">
-        <v>20.8</v>
+      <c r="L66" s="9">
+        <v>23.3</v>
       </c>
       <c r="M66" s="9">
-        <v>2777</v>
-      </c>
-      <c r="N66" s="10">
-        <v>1.42</v>
-      </c>
-      <c r="O66" s="9">
-        <v>0.62</v>
+        <v>541</v>
+      </c>
+      <c r="N66" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="O66" s="10">
+        <v>0.45</v>
       </c>
       <c r="P66" s="9">
-        <v>14</v>
-      </c>
-      <c r="Q66" s="10">
-        <v>1.0804</v>
+        <v>28.2</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>0.7422</v>
       </c>
       <c r="R66" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S66" s="9">
-        <v>54</v>
+      <c r="S66" s="10">
+        <v>44</v>
       </c>
       <c r="U66" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X66" s="11">
+      <c r="V66" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W66" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X66" s="12">
         <v>0</v>
       </c>
       <c r="Z66" s="5" t="inlineStr">
@@ -6831,7 +6854,7 @@
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -6840,26 +6863,26 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D67" s="6">
         <v>2014</v>
       </c>
       <c r="E67" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F67" s="7">
-        <v>41907</v>
+        <v>41872</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>0266</t>
+          <t>0229</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -6868,53 +6891,53 @@
         </is>
       </c>
       <c r="J67" s="8">
-        <v>0.427083333333333</v>
+        <v>0.667361111111111</v>
       </c>
       <c r="K67" s="9">
-        <v>8.2296</v>
-      </c>
-      <c r="L67" s="10">
-        <v>21</v>
+        <v>9.144</v>
+      </c>
+      <c r="L67" s="9">
+        <v>23.3</v>
       </c>
       <c r="M67" s="9">
-        <v>2639</v>
-      </c>
-      <c r="N67" s="10">
-        <v>1.34</v>
-      </c>
-      <c r="O67" s="9">
-        <v>0.48</v>
+        <v>541</v>
+      </c>
+      <c r="N67" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="O67" s="10">
+        <v>0.45</v>
       </c>
       <c r="P67" s="9">
-        <v>23.3</v>
-      </c>
-      <c r="Q67" s="10">
-        <v>1.0804</v>
+        <v>28.2</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>1.1469</v>
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S67" s="9">
-        <v>54</v>
+      <c r="S67" s="10">
+        <v>52</v>
       </c>
       <c r="U67" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W67" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X67" s="11">
+      <c r="V67" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W67" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X67" s="12">
         <v>0</v>
       </c>
       <c r="Z67" s="5" t="inlineStr">
@@ -6934,7 +6957,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D68" s="6">
@@ -6962,27 +6985,27 @@
         </is>
       </c>
       <c r="J68" s="8">
-        <v>0.472222222222222</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="K68" s="9">
-        <v>7.3152</v>
-      </c>
-      <c r="L68" s="10">
-        <v>21.5</v>
+        <v>9.144</v>
+      </c>
+      <c r="L68" s="9">
+        <v>20.8</v>
       </c>
       <c r="M68" s="9">
-        <v>1515</v>
-      </c>
-      <c r="N68" s="10">
-        <v>0.74</v>
-      </c>
-      <c r="O68" s="9">
-        <v>0.53</v>
+        <v>2777</v>
+      </c>
+      <c r="N68" s="9">
+        <v>1.42</v>
+      </c>
+      <c r="O68" s="10">
+        <v>0.62</v>
       </c>
       <c r="P68" s="9">
-        <v>23.4</v>
-      </c>
-      <c r="Q68" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q68" s="9">
         <v>1.0804</v>
       </c>
       <c r="R68" s="5" t="inlineStr">
@@ -6990,7 +7013,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S68" s="9">
+      <c r="S68" s="10">
         <v>54</v>
       </c>
       <c r="U68" s="5" t="inlineStr">
@@ -6998,17 +7021,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V68" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W68" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X68" s="11">
+      <c r="V68" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W68" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X68" s="12">
         <v>0</v>
       </c>
       <c r="Z68" s="5" t="inlineStr">
@@ -7061,22 +7084,22 @@
       <c r="K69" s="9">
         <v>6.4008</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="9">
         <v>20.9</v>
       </c>
       <c r="M69" s="9">
         <v>3134</v>
       </c>
-      <c r="N69" s="10">
+      <c r="N69" s="9">
         <v>1.61</v>
       </c>
-      <c r="O69" s="9">
+      <c r="O69" s="10">
         <v>0.47</v>
       </c>
       <c r="P69" s="9">
         <v>24.4</v>
       </c>
-      <c r="Q69" s="10">
+      <c r="Q69" s="9">
         <v>1.0804</v>
       </c>
       <c r="R69" s="5" t="inlineStr">
@@ -7084,7 +7107,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S69" s="9">
+      <c r="S69" s="10">
         <v>54</v>
       </c>
       <c r="U69" s="5" t="inlineStr">
@@ -7092,17 +7115,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V69" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W69" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X69" s="11">
+      <c r="V69" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W69" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X69" s="12">
         <v>0</v>
       </c>
       <c r="Z69" s="5" t="inlineStr">
@@ -7150,27 +7173,27 @@
         </is>
       </c>
       <c r="J70" s="8">
-        <v>0.45</v>
+        <v>0.427083333333333</v>
       </c>
       <c r="K70" s="9">
-        <v>9.4488</v>
-      </c>
-      <c r="L70" s="10">
-        <v>21.3</v>
+        <v>8.2296</v>
+      </c>
+      <c r="L70" s="9">
+        <v>21</v>
       </c>
       <c r="M70" s="9">
-        <v>1975</v>
-      </c>
-      <c r="N70" s="10">
-        <v>0.98</v>
-      </c>
-      <c r="O70" s="9">
-        <v>0.42</v>
+        <v>2639</v>
+      </c>
+      <c r="N70" s="9">
+        <v>1.34</v>
+      </c>
+      <c r="O70" s="10">
+        <v>0.48</v>
       </c>
       <c r="P70" s="9">
-        <v>30.6</v>
-      </c>
-      <c r="Q70" s="10">
+        <v>23.3</v>
+      </c>
+      <c r="Q70" s="9">
         <v>1.0804</v>
       </c>
       <c r="R70" s="5" t="inlineStr">
@@ -7178,7 +7201,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="S70" s="9">
+      <c r="S70" s="10">
         <v>54</v>
       </c>
       <c r="U70" s="5" t="inlineStr">
@@ -7186,17 +7209,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V70" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W70" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X70" s="11">
+      <c r="V70" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W70" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X70" s="12">
         <v>0</v>
       </c>
       <c r="Z70" s="5" t="inlineStr">
@@ -7207,35 +7230,35 @@
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4">
-        <v>2109</v>
+        <v>2010</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>GES</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>TWNET</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D71" s="6">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E71" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F71" s="7">
-        <v>42969</v>
+        <v>41907</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>0266</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -7244,53 +7267,53 @@
         </is>
       </c>
       <c r="J71" s="8">
-        <v>0.450694444444444</v>
+        <v>0.45</v>
       </c>
       <c r="K71" s="9">
-        <v>1.524</v>
-      </c>
-      <c r="L71" s="10">
-        <v>19.6</v>
+        <v>9.4488</v>
+      </c>
+      <c r="L71" s="9">
+        <v>21.3</v>
       </c>
       <c r="M71" s="9">
-        <v>10907</v>
-      </c>
-      <c r="N71" s="10">
-        <v>6.17</v>
-      </c>
-      <c r="O71" s="9">
-        <v>16</v>
+        <v>1975</v>
+      </c>
+      <c r="N71" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="O71" s="10">
+        <v>0.42</v>
       </c>
       <c r="P71" s="9">
-        <v>166</v>
-      </c>
-      <c r="Q71" s="10">
-        <v>1.5419</v>
+        <v>30.6</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>1.0804</v>
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S71" s="9">
-        <v>65</v>
+      <c r="S71" s="10">
+        <v>54</v>
       </c>
       <c r="U71" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V71" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W71" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X71" s="11">
+      <c r="V71" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W71" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X71" s="12">
         <v>0</v>
       </c>
       <c r="Z71" s="5" t="inlineStr">
@@ -7301,35 +7324,35 @@
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4">
-        <v>2129</v>
+        <v>2010</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>FMWT</t>
+          <t>GES</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>MWT</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D72" s="6">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E72" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F72" s="7">
-        <v>43018</v>
+        <v>41907</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>0266</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -7338,53 +7361,53 @@
         </is>
       </c>
       <c r="J72" s="8">
-        <v>0.334722222222222</v>
+        <v>0.472222222222222</v>
       </c>
       <c r="K72" s="9">
-        <v>12.192</v>
-      </c>
-      <c r="L72" s="10">
-        <v>17.5</v>
+        <v>7.3152</v>
+      </c>
+      <c r="L72" s="9">
+        <v>21.5</v>
       </c>
       <c r="M72" s="9">
-        <v>1529</v>
-      </c>
-      <c r="N72" s="10">
-        <v>0.747074510833752</v>
-      </c>
-      <c r="O72" s="9">
-        <v>37.0000004768372</v>
+        <v>1515</v>
+      </c>
+      <c r="N72" s="9">
+        <v>0.74</v>
+      </c>
+      <c r="O72" s="10">
+        <v>0.53</v>
       </c>
       <c r="P72" s="9">
-        <v>29.9</v>
-      </c>
-      <c r="Q72" s="10">
-        <v>0.4965</v>
+        <v>23.4</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>1.0804</v>
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S72" s="9">
-        <v>42</v>
+      <c r="S72" s="10">
+        <v>54</v>
       </c>
       <c r="U72" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V72" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W72" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X72" s="11">
+      <c r="V72" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W72" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X72" s="12">
         <v>0</v>
       </c>
       <c r="Z72" s="5" t="inlineStr">
@@ -7395,35 +7418,35 @@
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4">
-        <v>2129</v>
+        <v>2109</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>FMWT</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>MWT</t>
+          <t>TWNET</t>
         </is>
       </c>
       <c r="D73" s="6">
         <v>2017</v>
       </c>
       <c r="E73" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F73" s="7">
-        <v>43018</v>
+        <v>42969</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -7432,53 +7455,53 @@
         </is>
       </c>
       <c r="J73" s="8">
-        <v>0.334722222222222</v>
+        <v>0.450694444444444</v>
       </c>
       <c r="K73" s="9">
-        <v>12.192</v>
-      </c>
-      <c r="L73" s="10">
-        <v>17.5</v>
+        <v>1.524</v>
+      </c>
+      <c r="L73" s="9">
+        <v>19.6</v>
       </c>
       <c r="M73" s="9">
-        <v>1529</v>
-      </c>
-      <c r="N73" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="O73" s="9">
-        <v>37</v>
+        <v>10907</v>
+      </c>
+      <c r="N73" s="9">
+        <v>6.17</v>
+      </c>
+      <c r="O73" s="10">
+        <v>16</v>
       </c>
       <c r="P73" s="9">
-        <v>29.9</v>
-      </c>
-      <c r="Q73" s="10">
-        <v>0.4965</v>
+        <v>166</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>1.5419</v>
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S73" s="9">
-        <v>42</v>
+      <c r="S73" s="10">
+        <v>65</v>
       </c>
       <c r="U73" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V73" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W73" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X73" s="11">
+      <c r="V73" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W73" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X73" s="12">
         <v>0</v>
       </c>
       <c r="Z73" s="5" t="inlineStr">
@@ -7489,35 +7512,35 @@
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4">
-        <v>2250</v>
+        <v>2129</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>SKT</t>
+          <t>FMWT</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>MWT</t>
         </is>
       </c>
       <c r="D74" s="6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E74" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F74" s="7">
-        <v>42712</v>
+        <v>43018</v>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>701</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>7361</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -7526,53 +7549,53 @@
         </is>
       </c>
       <c r="J74" s="8">
-        <v>0.350694444444444</v>
+        <v>0.334722222222222</v>
       </c>
       <c r="K74" s="9">
-        <v>7.0104</v>
-      </c>
-      <c r="L74" s="10">
-        <v>9.5</v>
+        <v>12.192</v>
+      </c>
+      <c r="L74" s="9">
+        <v>17.5</v>
       </c>
       <c r="M74" s="9">
-        <v>244</v>
-      </c>
-      <c r="N74" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="O74" s="9">
-        <v>56</v>
+        <v>1529</v>
+      </c>
+      <c r="N74" s="9">
+        <v>0.747074510833752</v>
+      </c>
+      <c r="O74" s="10">
+        <v>37.0000004768372</v>
       </c>
       <c r="P74" s="9">
-        <v>22</v>
-      </c>
-      <c r="Q74" s="10">
-        <v>1.71025</v>
+        <v>29.9</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>0.4965</v>
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S74" s="9">
-        <v>63.2</v>
+      <c r="S74" s="10">
+        <v>42</v>
       </c>
       <c r="U74" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V74" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W74" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X74" s="11">
+      <c r="V74" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W74" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X74" s="12">
         <v>0</v>
       </c>
       <c r="Z74" s="5" t="inlineStr">
@@ -7583,7 +7606,7 @@
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
@@ -7625,48 +7648,48 @@
       <c r="K75" s="9">
         <v>7.0104</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L75" s="9">
         <v>9.5</v>
       </c>
       <c r="M75" s="9">
         <v>244</v>
       </c>
-      <c r="N75" s="10">
+      <c r="N75" s="9">
         <v>0.1</v>
       </c>
-      <c r="O75" s="9">
+      <c r="O75" s="10">
         <v>56</v>
       </c>
       <c r="P75" s="9">
         <v>22</v>
       </c>
-      <c r="Q75" s="10">
-        <v>1.67681</v>
+      <c r="Q75" s="9">
+        <v>1.71025</v>
       </c>
       <c r="R75" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S75" s="9">
-        <v>61.5</v>
+      <c r="S75" s="10">
+        <v>63.2</v>
       </c>
       <c r="U75" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V75" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W75" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X75" s="11">
+      <c r="V75" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W75" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X75" s="12">
         <v>0</v>
       </c>
       <c r="Z75" s="5" t="inlineStr">
@@ -7677,7 +7700,7 @@
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
@@ -7719,51 +7742,145 @@
       <c r="K76" s="9">
         <v>7.0104</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L76" s="9">
         <v>9.5</v>
       </c>
       <c r="M76" s="9">
         <v>244</v>
       </c>
-      <c r="N76" s="10">
+      <c r="N76" s="9">
         <v>0.1</v>
       </c>
-      <c r="O76" s="9">
+      <c r="O76" s="10">
         <v>56</v>
       </c>
       <c r="P76" s="9">
         <v>22</v>
       </c>
-      <c r="Q76" s="10">
+      <c r="Q76" s="9">
+        <v>1.67681</v>
+      </c>
+      <c r="R76" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S76" s="10">
+        <v>61.5</v>
+      </c>
+      <c r="U76" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V76" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W76" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="77">
+      <c r="A77" s="4">
+        <v>2255</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D77" s="6">
+        <v>2016</v>
+      </c>
+      <c r="E77" s="6">
+        <v>12</v>
+      </c>
+      <c r="F77" s="7">
+        <v>42712</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>DELSME</t>
+        </is>
+      </c>
+      <c r="J77" s="8">
+        <v>0.350694444444444</v>
+      </c>
+      <c r="K77" s="9">
+        <v>7.0104</v>
+      </c>
+      <c r="L77" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="M77" s="9">
+        <v>244</v>
+      </c>
+      <c r="N77" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="O77" s="10">
+        <v>56</v>
+      </c>
+      <c r="P77" s="9">
+        <v>22</v>
+      </c>
+      <c r="Q77" s="9">
         <v>1.34281</v>
       </c>
-      <c r="R76" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S76" s="9">
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S77" s="10">
         <v>59.1</v>
       </c>
-      <c r="U76" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V76" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W76" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X76" s="11">
+      <c r="U77" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V77" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W77" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X77" s="12">
         <v>0</v>
       </c>
-      <c r="Z76" s="5" t="inlineStr">
+      <c r="Z77" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
+++ b/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
@@ -888,7 +888,7 @@
       <c r="N2" s="9">
         <v>5.91239763594603</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="9">
         <v>27</v>
       </c>
       <c r="P2" s="9">
@@ -976,7 +976,7 @@
       <c r="N3" s="9">
         <v>7.61106010654548</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>46</v>
       </c>
       <c r="P3" s="9">
@@ -1067,7 +1067,7 @@
       <c r="N4" s="9">
         <v>8.93932597090552</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>66</v>
       </c>
       <c r="P4" s="9">
@@ -1158,7 +1158,7 @@
       <c r="N5" s="9">
         <v>0.233956419909353</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="9">
         <v>17</v>
       </c>
       <c r="P5" s="9">
@@ -1249,7 +1249,7 @@
       <c r="N6" s="9">
         <v>0.29</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="9">
         <v>43</v>
       </c>
       <c r="P6" s="9">
@@ -1340,7 +1340,7 @@
       <c r="N7" s="9">
         <v>0.56</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <v>20</v>
       </c>
       <c r="P7" s="9">
@@ -1431,7 +1431,7 @@
       <c r="N8" s="9">
         <v>0.56</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>20</v>
       </c>
       <c r="P8" s="9">
@@ -1522,7 +1522,7 @@
       <c r="N9" s="9">
         <v>0.07</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="9">
         <v>81</v>
       </c>
       <c r="P9" s="9">
@@ -1613,7 +1613,7 @@
       <c r="N10" s="9">
         <v>0.14</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="9">
         <v>34</v>
       </c>
       <c r="P10" s="9">
@@ -1704,7 +1704,7 @@
       <c r="N11" s="9">
         <v>0.08</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="9">
         <v>32</v>
       </c>
       <c r="P11" s="9">
@@ -1795,7 +1795,7 @@
       <c r="N12" s="9">
         <v>0.116266663217221</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9">
         <v>72</v>
       </c>
       <c r="P12" s="9">
@@ -1889,7 +1889,7 @@
       <c r="N13" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="9">
         <v>40</v>
       </c>
       <c r="Q13" s="9">
@@ -1980,7 +1980,7 @@
       <c r="N14" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>40</v>
       </c>
       <c r="Q14" s="9">
@@ -2071,7 +2071,7 @@
       <c r="N15" s="9">
         <v>6.57823246724982</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="9">
         <v>22</v>
       </c>
       <c r="Q15" s="9">
@@ -2162,7 +2162,7 @@
       <c r="N16" s="9">
         <v>4.22113673098982</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="9">
         <v>30</v>
       </c>
       <c r="Q16" s="9">
@@ -2253,7 +2253,7 @@
       <c r="N17" s="9">
         <v>0.714149189200495</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>27</v>
       </c>
       <c r="Q17" s="9">
@@ -2344,7 +2344,7 @@
       <c r="N18" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
@@ -2435,7 +2435,7 @@
       <c r="N19" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
@@ -2526,7 +2526,7 @@
       <c r="N20" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>44</v>
       </c>
       <c r="P20" s="9">
@@ -2620,7 +2620,7 @@
       <c r="N21" s="9">
         <v>0.628411617</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="9">
         <v>20</v>
       </c>
       <c r="P21" s="9">
@@ -2714,7 +2714,7 @@
       <c r="N22" s="9">
         <v>2.243137285</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="9">
         <v>27</v>
       </c>
       <c r="P22" s="9">
@@ -2808,7 +2808,7 @@
       <c r="N23" s="9">
         <v>0.751786255</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="9">
         <v>17</v>
       </c>
       <c r="P23" s="9">
@@ -2902,7 +2902,7 @@
       <c r="N24" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="9">
         <v>44</v>
       </c>
       <c r="P24" s="9">
@@ -2996,7 +2996,7 @@
       <c r="N25" s="9">
         <v>7.07014200626035E-02</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="9">
         <v>43</v>
       </c>
       <c r="Q25" s="9">
@@ -3087,7 +3087,7 @@
       <c r="N26" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="9">
         <v>19</v>
       </c>
       <c r="Q26" s="9">
@@ -3184,7 +3184,7 @@
       <c r="N27" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="9">
         <v>19</v>
       </c>
       <c r="Q27" s="9">
@@ -3275,7 +3275,7 @@
       <c r="N28" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="9">
         <v>19</v>
       </c>
       <c r="Q28" s="9">
@@ -3366,7 +3366,7 @@
       <c r="N29" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="9">
         <v>18</v>
       </c>
       <c r="Q29" s="9">
@@ -3457,7 +3457,7 @@
       <c r="N30" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="9">
         <v>18</v>
       </c>
       <c r="Q30" s="9">
@@ -3548,7 +3548,7 @@
       <c r="N31" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O31" s="9">
         <v>18</v>
       </c>
       <c r="Q31" s="9">
@@ -3639,7 +3639,7 @@
       <c r="N32" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O32" s="9">
         <v>18</v>
       </c>
       <c r="Q32" s="9">
@@ -3730,7 +3730,7 @@
       <c r="N33" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O33" s="10">
+      <c r="O33" s="9">
         <v>10</v>
       </c>
       <c r="Q33" s="9">
@@ -3821,7 +3821,7 @@
       <c r="N34" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O34" s="10">
+      <c r="O34" s="9">
         <v>10</v>
       </c>
       <c r="Q34" s="9">
@@ -3912,7 +3912,7 @@
       <c r="N35" s="9">
         <v>0.146101890125461</v>
       </c>
-      <c r="O35" s="10">
+      <c r="O35" s="9">
         <v>63</v>
       </c>
       <c r="Q35" s="9">
@@ -4003,7 +4003,7 @@
       <c r="N36" s="9">
         <v>0.339467723207604</v>
       </c>
-      <c r="O36" s="10">
+      <c r="O36" s="9">
         <v>33</v>
       </c>
       <c r="P36" s="9">
@@ -4097,7 +4097,7 @@
       <c r="N37" s="9">
         <v>0.958821325062239</v>
       </c>
-      <c r="O37" s="10">
+      <c r="O37" s="9">
         <v>36</v>
       </c>
       <c r="P37" s="9">
@@ -4191,7 +4191,7 @@
       <c r="N38" s="9">
         <v>3.55899409093209</v>
       </c>
-      <c r="O38" s="10">
+      <c r="O38" s="9">
         <v>30</v>
       </c>
       <c r="P38" s="9">
@@ -4285,7 +4285,7 @@
       <c r="N39" s="9">
         <v>1.17275584161783</v>
       </c>
-      <c r="O39" s="10">
+      <c r="O39" s="9">
         <v>49.0000009536743</v>
       </c>
       <c r="P39" s="9">
@@ -4379,7 +4379,7 @@
       <c r="N40" s="9">
         <v>8.96570505211038E-02</v>
       </c>
-      <c r="O40" s="10">
+      <c r="O40" s="9">
         <v>38</v>
       </c>
       <c r="P40" s="9">
@@ -4473,7 +4473,7 @@
       <c r="N41" s="9">
         <v>0.754928529738625</v>
       </c>
-      <c r="O41" s="10">
+      <c r="O41" s="9">
         <v>48</v>
       </c>
       <c r="P41" s="9">
@@ -4567,7 +4567,7 @@
       <c r="N42" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O42" s="10">
+      <c r="O42" s="9">
         <v>41</v>
       </c>
       <c r="P42" s="9">
@@ -4661,7 +4661,7 @@
       <c r="N43" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O43" s="10">
+      <c r="O43" s="9">
         <v>41</v>
       </c>
       <c r="P43" s="9">
@@ -4755,7 +4755,7 @@
       <c r="N44" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O44" s="10">
+      <c r="O44" s="9">
         <v>36</v>
       </c>
       <c r="P44" s="9">
@@ -4849,7 +4849,7 @@
       <c r="N45" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O45" s="10">
+      <c r="O45" s="9">
         <v>36</v>
       </c>
       <c r="P45" s="9">
@@ -4943,7 +4943,7 @@
       <c r="N46" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O46" s="10">
+      <c r="O46" s="9">
         <v>36</v>
       </c>
       <c r="P46" s="9">
@@ -5037,7 +5037,7 @@
       <c r="N47" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O47" s="10">
+      <c r="O47" s="9">
         <v>37</v>
       </c>
       <c r="P47" s="9">
@@ -5131,7 +5131,7 @@
       <c r="N48" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O48" s="10">
+      <c r="O48" s="9">
         <v>37</v>
       </c>
       <c r="P48" s="9">
@@ -5225,7 +5225,7 @@
       <c r="N49" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O49" s="10">
+      <c r="O49" s="9">
         <v>39</v>
       </c>
       <c r="P49" s="9">
@@ -5319,7 +5319,7 @@
       <c r="N50" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O50" s="10">
+      <c r="O50" s="9">
         <v>39</v>
       </c>
       <c r="P50" s="9">
@@ -5413,7 +5413,7 @@
       <c r="N51" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O51" s="10">
+      <c r="O51" s="9">
         <v>21</v>
       </c>
       <c r="P51" s="9">
@@ -5507,7 +5507,7 @@
       <c r="N52" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O52" s="10">
+      <c r="O52" s="9">
         <v>21</v>
       </c>
       <c r="P52" s="9">
@@ -5601,7 +5601,7 @@
       <c r="N53" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O53" s="10">
+      <c r="O53" s="9">
         <v>21</v>
       </c>
       <c r="P53" s="9">
@@ -5695,7 +5695,7 @@
       <c r="N54" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O54" s="10">
+      <c r="O54" s="9">
         <v>21</v>
       </c>
       <c r="P54" s="9">
@@ -5789,7 +5789,7 @@
       <c r="N55" s="9">
         <v>0.07</v>
       </c>
-      <c r="O55" s="10">
+      <c r="O55" s="9">
         <v>12</v>
       </c>
       <c r="P55" s="9">
@@ -5880,7 +5880,7 @@
       <c r="N56" s="9">
         <v>0.6</v>
       </c>
-      <c r="O56" s="10">
+      <c r="O56" s="9">
         <v>0.6</v>
       </c>
       <c r="P56" s="9">
@@ -5971,7 +5971,7 @@
       <c r="N57" s="9">
         <v>0.6</v>
       </c>
-      <c r="O57" s="10">
+      <c r="O57" s="9">
         <v>0.6</v>
       </c>
       <c r="P57" s="9">
@@ -6062,7 +6062,7 @@
       <c r="N58" s="9">
         <v>2.32</v>
       </c>
-      <c r="O58" s="10">
+      <c r="O58" s="9">
         <v>0.59</v>
       </c>
       <c r="P58" s="9">
@@ -6156,7 +6156,7 @@
       <c r="N59" s="9">
         <v>0.58</v>
       </c>
-      <c r="O59" s="10">
+      <c r="O59" s="9">
         <v>0.66</v>
       </c>
       <c r="P59" s="9">
@@ -6250,7 +6250,7 @@
       <c r="N60" s="9">
         <v>1.03</v>
       </c>
-      <c r="O60" s="10">
+      <c r="O60" s="9">
         <v>0.54</v>
       </c>
       <c r="P60" s="9">
@@ -6344,7 +6344,7 @@
       <c r="N61" s="9">
         <v>1.63</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O61" s="9">
         <v>0.57</v>
       </c>
       <c r="P61" s="9">
@@ -6435,7 +6435,7 @@
       <c r="N62" s="9">
         <v>2.32</v>
       </c>
-      <c r="O62" s="10">
+      <c r="O62" s="9">
         <v>0.59</v>
       </c>
       <c r="P62" s="9">
@@ -6529,7 +6529,7 @@
       <c r="N63" s="9">
         <v>0.58</v>
       </c>
-      <c r="O63" s="10">
+      <c r="O63" s="9">
         <v>0.66</v>
       </c>
       <c r="P63" s="9">
@@ -6623,7 +6623,7 @@
       <c r="N64" s="9">
         <v>1.03</v>
       </c>
-      <c r="O64" s="10">
+      <c r="O64" s="9">
         <v>0.54</v>
       </c>
       <c r="P64" s="9">
@@ -6717,7 +6717,7 @@
       <c r="N65" s="9">
         <v>1.63</v>
       </c>
-      <c r="O65" s="10">
+      <c r="O65" s="9">
         <v>0.57</v>
       </c>
       <c r="P65" s="9">
@@ -6811,7 +6811,7 @@
       <c r="N66" s="9">
         <v>0.25</v>
       </c>
-      <c r="O66" s="10">
+      <c r="O66" s="9">
         <v>0.45</v>
       </c>
       <c r="P66" s="9">
@@ -6905,7 +6905,7 @@
       <c r="N67" s="9">
         <v>0.25</v>
       </c>
-      <c r="O67" s="10">
+      <c r="O67" s="9">
         <v>0.45</v>
       </c>
       <c r="P67" s="9">
@@ -6999,7 +6999,7 @@
       <c r="N68" s="9">
         <v>1.42</v>
       </c>
-      <c r="O68" s="10">
+      <c r="O68" s="9">
         <v>0.62</v>
       </c>
       <c r="P68" s="9">
@@ -7093,7 +7093,7 @@
       <c r="N69" s="9">
         <v>1.61</v>
       </c>
-      <c r="O69" s="10">
+      <c r="O69" s="9">
         <v>0.47</v>
       </c>
       <c r="P69" s="9">
@@ -7187,7 +7187,7 @@
       <c r="N70" s="9">
         <v>1.34</v>
       </c>
-      <c r="O70" s="10">
+      <c r="O70" s="9">
         <v>0.48</v>
       </c>
       <c r="P70" s="9">
@@ -7281,7 +7281,7 @@
       <c r="N71" s="9">
         <v>0.98</v>
       </c>
-      <c r="O71" s="10">
+      <c r="O71" s="9">
         <v>0.42</v>
       </c>
       <c r="P71" s="9">
@@ -7375,7 +7375,7 @@
       <c r="N72" s="9">
         <v>0.74</v>
       </c>
-      <c r="O72" s="10">
+      <c r="O72" s="9">
         <v>0.53</v>
       </c>
       <c r="P72" s="9">
@@ -7469,7 +7469,7 @@
       <c r="N73" s="9">
         <v>6.17</v>
       </c>
-      <c r="O73" s="10">
+      <c r="O73" s="9">
         <v>16</v>
       </c>
       <c r="P73" s="9">
@@ -7563,7 +7563,7 @@
       <c r="N74" s="9">
         <v>0.747074510833752</v>
       </c>
-      <c r="O74" s="10">
+      <c r="O74" s="9">
         <v>37.0000004768372</v>
       </c>
       <c r="P74" s="9">
@@ -7657,7 +7657,7 @@
       <c r="N75" s="9">
         <v>0.1</v>
       </c>
-      <c r="O75" s="10">
+      <c r="O75" s="9">
         <v>56</v>
       </c>
       <c r="P75" s="9">
@@ -7751,7 +7751,7 @@
       <c r="N76" s="9">
         <v>0.1</v>
       </c>
-      <c r="O76" s="10">
+      <c r="O76" s="9">
         <v>56</v>
       </c>
       <c r="P76" s="9">
@@ -7845,7 +7845,7 @@
       <c r="N77" s="9">
         <v>0.1</v>
       </c>
-      <c r="O77" s="10">
+      <c r="O77" s="9">
         <v>56</v>
       </c>
       <c r="P77" s="9">

--- a/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
+++ b/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
@@ -888,7 +888,7 @@
       <c r="N2" s="9">
         <v>5.91239763594603</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="10">
         <v>27</v>
       </c>
       <c r="P2" s="9">
@@ -976,7 +976,7 @@
       <c r="N3" s="9">
         <v>7.61106010654548</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="10">
         <v>46</v>
       </c>
       <c r="P3" s="9">
@@ -1067,7 +1067,7 @@
       <c r="N4" s="9">
         <v>8.93932597090552</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="10">
         <v>66</v>
       </c>
       <c r="P4" s="9">
@@ -1158,7 +1158,7 @@
       <c r="N5" s="9">
         <v>0.233956419909353</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="10">
         <v>17</v>
       </c>
       <c r="P5" s="9">
@@ -1249,7 +1249,7 @@
       <c r="N6" s="9">
         <v>0.29</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="10">
         <v>43</v>
       </c>
       <c r="P6" s="9">
@@ -1340,7 +1340,7 @@
       <c r="N7" s="9">
         <v>0.56</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="10">
         <v>20</v>
       </c>
       <c r="P7" s="9">
@@ -1431,7 +1431,7 @@
       <c r="N8" s="9">
         <v>0.56</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="10">
         <v>20</v>
       </c>
       <c r="P8" s="9">
@@ -1522,7 +1522,7 @@
       <c r="N9" s="9">
         <v>0.07</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <v>81</v>
       </c>
       <c r="P9" s="9">
@@ -1613,7 +1613,7 @@
       <c r="N10" s="9">
         <v>0.14</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="10">
         <v>34</v>
       </c>
       <c r="P10" s="9">
@@ -1704,7 +1704,7 @@
       <c r="N11" s="9">
         <v>0.08</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="10">
         <v>32</v>
       </c>
       <c r="P11" s="9">
@@ -1795,7 +1795,7 @@
       <c r="N12" s="9">
         <v>0.116266663217221</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="10">
         <v>72</v>
       </c>
       <c r="P12" s="9">
@@ -1889,7 +1889,7 @@
       <c r="N13" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="10">
         <v>40</v>
       </c>
       <c r="Q13" s="9">
@@ -1980,7 +1980,7 @@
       <c r="N14" s="9">
         <v>4.30947075014608</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="10">
         <v>40</v>
       </c>
       <c r="Q14" s="9">
@@ -2071,7 +2071,7 @@
       <c r="N15" s="9">
         <v>6.57823246724982</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <v>22</v>
       </c>
       <c r="Q15" s="9">
@@ -2162,7 +2162,7 @@
       <c r="N16" s="9">
         <v>4.22113673098982</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <v>30</v>
       </c>
       <c r="Q16" s="9">
@@ -2253,7 +2253,7 @@
       <c r="N17" s="9">
         <v>0.714149189200495</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>27</v>
       </c>
       <c r="Q17" s="9">
@@ -2344,7 +2344,7 @@
       <c r="N18" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="10">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
@@ -2435,7 +2435,7 @@
       <c r="N19" s="9">
         <v>0.181581224941503</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="10">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
@@ -2526,7 +2526,7 @@
       <c r="N20" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="10">
         <v>44</v>
       </c>
       <c r="P20" s="9">
@@ -2620,7 +2620,7 @@
       <c r="N21" s="9">
         <v>0.628411617</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="10">
         <v>20</v>
       </c>
       <c r="P21" s="9">
@@ -2714,7 +2714,7 @@
       <c r="N22" s="9">
         <v>2.243137285</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="10">
         <v>27</v>
       </c>
       <c r="P22" s="9">
@@ -2808,7 +2808,7 @@
       <c r="N23" s="9">
         <v>0.751786255</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="10">
         <v>17</v>
       </c>
       <c r="P23" s="9">
@@ -2902,7 +2902,7 @@
       <c r="N24" s="9">
         <v>0.733996912617268</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="10">
         <v>44</v>
       </c>
       <c r="P24" s="9">
@@ -2996,7 +2996,7 @@
       <c r="N25" s="9">
         <v>7.07014200626035E-02</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="10">
         <v>43</v>
       </c>
       <c r="Q25" s="9">
@@ -3087,7 +3087,7 @@
       <c r="N26" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="10">
         <v>19</v>
       </c>
       <c r="Q26" s="9">
@@ -3184,7 +3184,7 @@
       <c r="N27" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="10">
         <v>19</v>
       </c>
       <c r="Q27" s="9">
@@ -3275,7 +3275,7 @@
       <c r="N28" s="9">
         <v>6.54016567157918</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="10">
         <v>19</v>
       </c>
       <c r="Q28" s="9">
@@ -3366,7 +3366,7 @@
       <c r="N29" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="10">
         <v>18</v>
       </c>
       <c r="Q29" s="9">
@@ -3457,7 +3457,7 @@
       <c r="N30" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="10">
         <v>18</v>
       </c>
       <c r="Q30" s="9">
@@ -3548,7 +3548,7 @@
       <c r="N31" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="10">
         <v>18</v>
       </c>
       <c r="Q31" s="9">
@@ -3639,7 +3639,7 @@
       <c r="N32" s="9">
         <v>9.16612204170404</v>
       </c>
-      <c r="O32" s="9">
+      <c r="O32" s="10">
         <v>18</v>
       </c>
       <c r="Q32" s="9">
@@ -3730,7 +3730,7 @@
       <c r="N33" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O33" s="10">
         <v>10</v>
       </c>
       <c r="Q33" s="9">
@@ -3821,7 +3821,7 @@
       <c r="N34" s="9">
         <v>10.4626731003908</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="10">
         <v>10</v>
       </c>
       <c r="Q34" s="9">
@@ -3912,7 +3912,7 @@
       <c r="N35" s="9">
         <v>0.146101890125461</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="10">
         <v>63</v>
       </c>
       <c r="Q35" s="9">
@@ -4003,7 +4003,7 @@
       <c r="N36" s="9">
         <v>0.339467723207604</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="10">
         <v>33</v>
       </c>
       <c r="P36" s="9">
@@ -4097,7 +4097,7 @@
       <c r="N37" s="9">
         <v>0.958821325062239</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="10">
         <v>36</v>
       </c>
       <c r="P37" s="9">
@@ -4191,7 +4191,7 @@
       <c r="N38" s="9">
         <v>3.55899409093209</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="10">
         <v>30</v>
       </c>
       <c r="P38" s="9">
@@ -4285,7 +4285,7 @@
       <c r="N39" s="9">
         <v>1.17275584161783</v>
       </c>
-      <c r="O39" s="9">
+      <c r="O39" s="10">
         <v>49.0000009536743</v>
       </c>
       <c r="P39" s="9">
@@ -4379,7 +4379,7 @@
       <c r="N40" s="9">
         <v>8.96570505211038E-02</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="10">
         <v>38</v>
       </c>
       <c r="P40" s="9">
@@ -4473,7 +4473,7 @@
       <c r="N41" s="9">
         <v>0.754928529738625</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="10">
         <v>48</v>
       </c>
       <c r="P41" s="9">
@@ -4567,7 +4567,7 @@
       <c r="N42" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="10">
         <v>41</v>
       </c>
       <c r="P42" s="9">
@@ -4661,7 +4661,7 @@
       <c r="N43" s="9">
         <v>1.70968314202846</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="10">
         <v>41</v>
       </c>
       <c r="P43" s="9">
@@ -4755,7 +4755,7 @@
       <c r="N44" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O44" s="9">
+      <c r="O44" s="10">
         <v>36</v>
       </c>
       <c r="P44" s="9">
@@ -4849,7 +4849,7 @@
       <c r="N45" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O45" s="10">
         <v>36</v>
       </c>
       <c r="P45" s="9">
@@ -4943,7 +4943,7 @@
       <c r="N46" s="9">
         <v>2.2160294728127</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O46" s="10">
         <v>36</v>
       </c>
       <c r="P46" s="9">
@@ -5037,7 +5037,7 @@
       <c r="N47" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O47" s="10">
         <v>37</v>
       </c>
       <c r="P47" s="9">
@@ -5131,7 +5131,7 @@
       <c r="N48" s="9">
         <v>1.75849732530641</v>
       </c>
-      <c r="O48" s="9">
+      <c r="O48" s="10">
         <v>37</v>
       </c>
       <c r="P48" s="9">
@@ -5225,7 +5225,7 @@
       <c r="N49" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O49" s="9">
+      <c r="O49" s="10">
         <v>39</v>
       </c>
       <c r="P49" s="9">
@@ -5319,7 +5319,7 @@
       <c r="N50" s="9">
         <v>0.189213103613724</v>
       </c>
-      <c r="O50" s="9">
+      <c r="O50" s="10">
         <v>39</v>
       </c>
       <c r="P50" s="9">
@@ -5413,7 +5413,7 @@
       <c r="N51" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O51" s="9">
+      <c r="O51" s="10">
         <v>21</v>
       </c>
       <c r="P51" s="9">
@@ -5507,7 +5507,7 @@
       <c r="N52" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O52" s="9">
+      <c r="O52" s="10">
         <v>21</v>
       </c>
       <c r="P52" s="9">
@@ -5601,7 +5601,7 @@
       <c r="N53" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O53" s="9">
+      <c r="O53" s="10">
         <v>21</v>
       </c>
       <c r="P53" s="9">
@@ -5695,7 +5695,7 @@
       <c r="N54" s="9">
         <v>10.9414851434528</v>
       </c>
-      <c r="O54" s="9">
+      <c r="O54" s="10">
         <v>21</v>
       </c>
       <c r="P54" s="9">
@@ -5789,7 +5789,7 @@
       <c r="N55" s="9">
         <v>0.07</v>
       </c>
-      <c r="O55" s="9">
+      <c r="O55" s="10">
         <v>12</v>
       </c>
       <c r="P55" s="9">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D56" s="6">
@@ -5880,7 +5880,7 @@
       <c r="N56" s="9">
         <v>0.6</v>
       </c>
-      <c r="O56" s="9">
+      <c r="O56" s="10">
         <v>0.6</v>
       </c>
       <c r="P56" s="9">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>FMWTCC</t>
+          <t>MWTCC</t>
         </is>
       </c>
       <c r="D57" s="6">
@@ -5971,7 +5971,7 @@
       <c r="N57" s="9">
         <v>0.6</v>
       </c>
-      <c r="O57" s="9">
+      <c r="O57" s="10">
         <v>0.6</v>
       </c>
       <c r="P57" s="9">
@@ -6062,7 +6062,7 @@
       <c r="N58" s="9">
         <v>2.32</v>
       </c>
-      <c r="O58" s="9">
+      <c r="O58" s="10">
         <v>0.59</v>
       </c>
       <c r="P58" s="9">
@@ -6156,7 +6156,7 @@
       <c r="N59" s="9">
         <v>0.58</v>
       </c>
-      <c r="O59" s="9">
+      <c r="O59" s="10">
         <v>0.66</v>
       </c>
       <c r="P59" s="9">
@@ -6250,7 +6250,7 @@
       <c r="N60" s="9">
         <v>1.03</v>
       </c>
-      <c r="O60" s="9">
+      <c r="O60" s="10">
         <v>0.54</v>
       </c>
       <c r="P60" s="9">
@@ -6344,7 +6344,7 @@
       <c r="N61" s="9">
         <v>1.63</v>
       </c>
-      <c r="O61" s="9">
+      <c r="O61" s="10">
         <v>0.57</v>
       </c>
       <c r="P61" s="9">
@@ -6435,7 +6435,7 @@
       <c r="N62" s="9">
         <v>2.32</v>
       </c>
-      <c r="O62" s="9">
+      <c r="O62" s="10">
         <v>0.59</v>
       </c>
       <c r="P62" s="9">
@@ -6529,7 +6529,7 @@
       <c r="N63" s="9">
         <v>0.58</v>
       </c>
-      <c r="O63" s="9">
+      <c r="O63" s="10">
         <v>0.66</v>
       </c>
       <c r="P63" s="9">
@@ -6623,7 +6623,7 @@
       <c r="N64" s="9">
         <v>1.03</v>
       </c>
-      <c r="O64" s="9">
+      <c r="O64" s="10">
         <v>0.54</v>
       </c>
       <c r="P64" s="9">
@@ -6717,7 +6717,7 @@
       <c r="N65" s="9">
         <v>1.63</v>
       </c>
-      <c r="O65" s="9">
+      <c r="O65" s="10">
         <v>0.57</v>
       </c>
       <c r="P65" s="9">
@@ -6811,7 +6811,7 @@
       <c r="N66" s="9">
         <v>0.25</v>
       </c>
-      <c r="O66" s="9">
+      <c r="O66" s="10">
         <v>0.45</v>
       </c>
       <c r="P66" s="9">
@@ -6905,7 +6905,7 @@
       <c r="N67" s="9">
         <v>0.25</v>
       </c>
-      <c r="O67" s="9">
+      <c r="O67" s="10">
         <v>0.45</v>
       </c>
       <c r="P67" s="9">
@@ -6999,7 +6999,7 @@
       <c r="N68" s="9">
         <v>1.42</v>
       </c>
-      <c r="O68" s="9">
+      <c r="O68" s="10">
         <v>0.62</v>
       </c>
       <c r="P68" s="9">
@@ -7093,7 +7093,7 @@
       <c r="N69" s="9">
         <v>1.61</v>
       </c>
-      <c r="O69" s="9">
+      <c r="O69" s="10">
         <v>0.47</v>
       </c>
       <c r="P69" s="9">
@@ -7187,7 +7187,7 @@
       <c r="N70" s="9">
         <v>1.34</v>
       </c>
-      <c r="O70" s="9">
+      <c r="O70" s="10">
         <v>0.48</v>
       </c>
       <c r="P70" s="9">
@@ -7281,7 +7281,7 @@
       <c r="N71" s="9">
         <v>0.98</v>
       </c>
-      <c r="O71" s="9">
+      <c r="O71" s="10">
         <v>0.42</v>
       </c>
       <c r="P71" s="9">
@@ -7375,7 +7375,7 @@
       <c r="N72" s="9">
         <v>0.74</v>
       </c>
-      <c r="O72" s="9">
+      <c r="O72" s="10">
         <v>0.53</v>
       </c>
       <c r="P72" s="9">
@@ -7469,7 +7469,7 @@
       <c r="N73" s="9">
         <v>6.17</v>
       </c>
-      <c r="O73" s="9">
+      <c r="O73" s="10">
         <v>16</v>
       </c>
       <c r="P73" s="9">
@@ -7563,7 +7563,7 @@
       <c r="N74" s="9">
         <v>0.747074510833752</v>
       </c>
-      <c r="O74" s="9">
+      <c r="O74" s="10">
         <v>37.0000004768372</v>
       </c>
       <c r="P74" s="9">
@@ -7657,7 +7657,7 @@
       <c r="N75" s="9">
         <v>0.1</v>
       </c>
-      <c r="O75" s="9">
+      <c r="O75" s="10">
         <v>56</v>
       </c>
       <c r="P75" s="9">
@@ -7751,7 +7751,7 @@
       <c r="N76" s="9">
         <v>0.1</v>
       </c>
-      <c r="O76" s="9">
+      <c r="O76" s="10">
         <v>56</v>
       </c>
       <c r="P76" s="9">
@@ -7845,7 +7845,7 @@
       <c r="N77" s="9">
         <v>0.1</v>
       </c>
-      <c r="O77" s="9">
+      <c r="O77" s="10">
         <v>56</v>
       </c>
       <c r="P77" s="9">

--- a/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
+++ b/Data for R/FLaSH/FLaSH EDI Qry_Empties with Enviro.xlsx
@@ -672,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.62109375"/>
@@ -701,6 +701,8 @@
     <col customWidth="true" min="24" max="24" width="14.0625"/>
     <col customWidth="true" min="25" max="25" width="13.76953125"/>
     <col customWidth="true" min="26" max="26" width="14.0625"/>
+    <col customWidth="true" min="27" max="27" width="10.10546875"/>
+    <col customWidth="true" min="28" max="28" width="10.984375"/>
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -834,6 +836,16 @@
           <t>CulturedOrigin</t>
         </is>
       </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>DietStudy</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>PreyItemsID'd</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="4">
@@ -922,6 +934,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="4">
@@ -1013,6 +1033,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="4">
@@ -1104,6 +1132,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="4">
@@ -1195,6 +1231,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA5" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="4">
@@ -1286,6 +1330,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="4">
@@ -1377,6 +1429,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA7" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="4">
@@ -1468,6 +1528,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="4">
@@ -1559,6 +1627,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="4">
@@ -1650,6 +1726,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="4">
@@ -1741,6 +1825,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA11" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="4">
@@ -1835,6 +1927,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="4">
@@ -1926,6 +2026,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4">
@@ -2017,6 +2125,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA14" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="4">
@@ -2108,6 +2224,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="4">
@@ -2199,6 +2323,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA16" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="4">
@@ -2290,6 +2422,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="4">
@@ -2381,6 +2521,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="4">
@@ -2472,6 +2620,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="4">
@@ -2566,6 +2722,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="4">
@@ -2660,6 +2824,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4">
@@ -2754,6 +2926,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA22" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4">
@@ -2848,6 +3028,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA23" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4">
@@ -2942,6 +3130,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA24" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4">
@@ -3033,6 +3229,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA25" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4">
@@ -3130,6 +3334,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA26" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="4">
@@ -3221,6 +3433,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA27" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4">
@@ -3312,6 +3532,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA28" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4">
@@ -3403,6 +3631,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA29" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4">
@@ -3494,6 +3730,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4">
@@ -3585,6 +3829,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA31" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4">
@@ -3676,6 +3928,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="4">
@@ -3767,6 +4027,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA33" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="4">
@@ -3858,6 +4126,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA34" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4">
@@ -3949,6 +4225,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA35" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="4">
@@ -4043,6 +4327,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA36" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="4">
@@ -4137,6 +4429,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="4">
@@ -4231,6 +4531,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA38" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4">
@@ -4325,6 +4633,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4">
@@ -4419,6 +4735,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA40" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4">
@@ -4513,6 +4837,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA41" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB41" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4">
@@ -4607,6 +4939,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA42" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4">
@@ -4701,6 +5041,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA43" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4">
@@ -4795,6 +5143,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA44" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4">
@@ -4889,6 +5245,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA45" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4">
@@ -4983,6 +5347,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA46" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4">
@@ -5077,6 +5449,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA47" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4">
@@ -5171,6 +5551,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA48" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4">
@@ -5265,6 +5653,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA49" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4">
@@ -5359,6 +5755,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA50" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4">
@@ -5453,6 +5857,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA51" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4">
@@ -5547,6 +5959,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA52" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4">
@@ -5641,6 +6061,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA53" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="4">
@@ -5735,6 +6163,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA54" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="4">
@@ -5829,6 +6265,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA55" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4">
@@ -5920,6 +6364,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA56" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="4">
@@ -6011,6 +6463,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA57" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="4">
@@ -6102,6 +6562,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA58" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4">
@@ -6196,6 +6664,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA59" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB59" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4">
@@ -6290,6 +6766,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA60" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4">
@@ -6384,6 +6868,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA61" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4">
@@ -6475,6 +6967,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA62" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4">
@@ -6569,6 +7069,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA63" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4">
@@ -6663,6 +7171,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA64" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4">
@@ -6757,6 +7273,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA65" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4">
@@ -6851,6 +7375,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA66" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4">
@@ -6945,6 +7477,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA67" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4">
@@ -7039,6 +7579,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA68" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4">
@@ -7133,6 +7681,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA69" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4">
@@ -7227,6 +7783,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA70" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4">
@@ -7321,6 +7885,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA71" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4">
@@ -7415,6 +7987,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA72" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4">
@@ -7509,6 +8089,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA73" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4">
@@ -7603,6 +8191,14 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AA74" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4">
@@ -7697,6 +8293,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AB75" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4">
@@ -7791,6 +8392,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AB76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4">
@@ -7883,6 +8489,11 @@
       <c r="Z77" s="5" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AB77" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
